--- a/附件.xlsx
+++ b/附件.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\华数杯\2026年第七届华数杯数学建模竞赛赛题\A题 微构体中填充导电介质的仿真优化\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A3D9C90-947F-4A3A-BF36-7AA629442F6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{A8C4CF2F-A132-4F64-BF71-2042DCBC8BBE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="15" yWindow="15" windowWidth="21585" windowHeight="13665" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -386,10 +386,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H14"/>
+  <dimension ref="A1:F14"/>
   <sheetFormatPr defaultRowHeight="13.9" x14ac:dyDescent="0.4"/>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -401,7 +401,7 @@
       <c r="E1" s="2"/>
       <c r="F1" s="2"/>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -421,7 +421,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A3">
         <v>-5000</v>
       </c>
@@ -440,12 +440,8 @@
       <c r="F3">
         <v>-256.91600475790102</v>
       </c>
-      <c r="H3">
-        <f>SQRT((D3-A3)^2+(E3-B3)^2+(F3-C3)^2)</f>
-        <v>2447.8138479470927</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A4">
         <v>-5000</v>
       </c>
@@ -464,12 +460,8 @@
       <c r="F4">
         <v>141.734026660795</v>
       </c>
-      <c r="H4">
-        <f t="shared" ref="H3:H14" si="0">SQRT((D4-A4)^2+(E4-B4)^2+(F4-C4)^2)</f>
-        <v>2315.5343698169572</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A5">
         <v>-5000</v>
       </c>
@@ -488,12 +480,8 @@
       <c r="F5">
         <v>-118.26517904821</v>
       </c>
-      <c r="H5">
-        <f t="shared" si="0"/>
-        <v>1062.1411789741362</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A6">
         <v>-4192.3186063671001</v>
       </c>
@@ -512,12 +500,8 @@
       <c r="F6">
         <v>-283.65102507075898</v>
       </c>
-      <c r="H6">
-        <f t="shared" si="0"/>
-        <v>5000.0000000000045</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A7">
         <v>-2777.9774379349601</v>
       </c>
@@ -536,12 +520,8 @@
       <c r="F7">
         <v>-280.70558480312201</v>
       </c>
-      <c r="H7">
-        <f t="shared" si="0"/>
-        <v>5000.0000000000018</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A8">
         <v>-2262.0395182923799</v>
       </c>
@@ -560,12 +540,8 @@
       <c r="F8">
         <v>500</v>
       </c>
-      <c r="H8">
-        <f t="shared" si="0"/>
-        <v>1419.6467067908795</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A9">
         <v>-843.854487636523</v>
       </c>
@@ -584,12 +560,8 @@
       <c r="F9">
         <v>-352.88610815190202</v>
       </c>
-      <c r="H9">
-        <f t="shared" si="0"/>
-        <v>3580.353293209118</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A10">
         <v>577.03807556830805</v>
       </c>
@@ -608,12 +580,8 @@
       <c r="F10">
         <v>-258.40355523640801</v>
       </c>
-      <c r="H10">
-        <f t="shared" si="0"/>
-        <v>4423.3115294642184</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A11">
         <v>1066.9641376733</v>
       </c>
@@ -632,12 +600,8 @@
       <c r="F11">
         <v>-144.67794013025599</v>
       </c>
-      <c r="H11">
-        <f t="shared" si="0"/>
-        <v>3937.8588210258636</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A12">
         <v>2330.7325351230602</v>
       </c>
@@ -656,12 +620,8 @@
       <c r="F12">
         <v>-45.535533422300396</v>
       </c>
-      <c r="H12">
-        <f t="shared" si="0"/>
-        <v>2684.4656301830446</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A13">
         <v>2656.5207249472501</v>
       </c>
@@ -680,12 +640,8 @@
       <c r="F13">
         <v>500</v>
       </c>
-      <c r="H13">
-        <f t="shared" si="0"/>
-        <v>1019.1172545934198</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A14">
         <v>3660.6880880437502</v>
       </c>
@@ -703,10 +659,6 @@
       </c>
       <c r="F14">
         <v>-413.21077078022</v>
-      </c>
-      <c r="H14">
-        <f t="shared" si="0"/>
-        <v>1359.2513846976615</v>
       </c>
     </row>
   </sheetData>
@@ -721,10 +673,10 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{35A61575-4DFF-4759-B038-95AFD1DDC398}">
-  <dimension ref="A1:H51"/>
+  <dimension ref="A1:F51"/>
   <sheetFormatPr defaultRowHeight="13.9" x14ac:dyDescent="0.4"/>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -736,7 +688,7 @@
       <c r="E1" s="2"/>
       <c r="F1" s="2"/>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -756,7 +708,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A3">
         <v>-5000</v>
       </c>
@@ -775,12 +727,8 @@
       <c r="F3">
         <v>-500</v>
       </c>
-      <c r="H3">
-        <f>SQRT((D3-A3)^2+(E3-B3)^2+(F3-C3)^2)</f>
-        <v>1506.0941803395392</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A4">
         <v>-5000</v>
       </c>
@@ -799,12 +747,8 @@
       <c r="F4">
         <v>-500</v>
       </c>
-      <c r="H4">
-        <f>SQRT((D4-A4)^2+(E4-B4)^2+(F4-C4)^2)</f>
-        <v>4230.1858498404708</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A5">
         <v>-5000</v>
       </c>
@@ -823,12 +767,8 @@
       <c r="F5">
         <v>318.20589464244802</v>
       </c>
-      <c r="H5">
-        <f t="shared" ref="H5:H52" si="0">SQRT((D5-A5)^2+(E5-B5)^2+(F5-C5)^2)</f>
-        <v>1844.6672446236553</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A6">
         <v>-5000</v>
       </c>
@@ -847,12 +787,8 @@
       <c r="F6">
         <v>-0.78688274292221705</v>
       </c>
-      <c r="H6">
-        <f t="shared" si="0"/>
-        <v>3080.1227520443604</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A7">
         <v>-5000</v>
       </c>
@@ -871,12 +807,8 @@
       <c r="F7">
         <v>-313.165070078707</v>
       </c>
-      <c r="H7">
-        <f t="shared" si="0"/>
-        <v>3017.1442233327843</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A8">
         <v>-5000</v>
       </c>
@@ -895,12 +827,8 @@
       <c r="F8">
         <v>297.87075428309703</v>
       </c>
-      <c r="H8">
-        <f t="shared" si="0"/>
-        <v>2677.2638185886635</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A9">
         <v>-5000</v>
       </c>
@@ -919,12 +847,8 @@
       <c r="F9">
         <v>171.71575876189399</v>
       </c>
-      <c r="H9">
-        <f t="shared" si="0"/>
-        <v>1556.487969694987</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A10">
         <v>-5000</v>
       </c>
@@ -943,12 +867,8 @@
       <c r="F10">
         <v>-500</v>
       </c>
-      <c r="H10">
-        <f t="shared" si="0"/>
-        <v>829.43838790071152</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A11">
         <v>-5000</v>
       </c>
@@ -967,12 +887,8 @@
       <c r="F11">
         <v>-500</v>
       </c>
-      <c r="H11">
-        <f t="shared" si="0"/>
-        <v>1944.0559972924643</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A12">
         <v>-5000</v>
       </c>
@@ -991,12 +907,8 @@
       <c r="F12">
         <v>218.05496070769499</v>
       </c>
-      <c r="H12">
-        <f t="shared" si="0"/>
-        <v>1874.6776896276024</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A13">
         <v>-5000</v>
       </c>
@@ -1015,12 +927,8 @@
       <c r="F13">
         <v>-325.954298674494</v>
       </c>
-      <c r="H13">
-        <f t="shared" si="0"/>
-        <v>3053.5735753661397</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A14">
         <v>-4850.2812675073801</v>
       </c>
@@ -1039,12 +947,8 @@
       <c r="F14">
         <v>-332.32330038417501</v>
       </c>
-      <c r="H14">
-        <f t="shared" si="0"/>
-        <v>5000.0000000000027</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A15">
         <v>-4467.8317733322501</v>
       </c>
@@ -1063,12 +967,8 @@
       <c r="F15">
         <v>398.70315840281103</v>
       </c>
-      <c r="H15">
-        <f t="shared" si="0"/>
-        <v>2967.3006364069115</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A16">
         <v>-4320.9778288983098</v>
       </c>
@@ -1087,12 +987,8 @@
       <c r="F16">
         <v>205.10787964037999</v>
       </c>
-      <c r="H16">
-        <f t="shared" si="0"/>
-        <v>4999.9999999999945</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A17">
         <v>-4173.9438452488303</v>
       </c>
@@ -1111,12 +1007,8 @@
       <c r="F17">
         <v>260.529013263423</v>
       </c>
-      <c r="H17">
-        <f t="shared" si="0"/>
-        <v>3716.8968047957146</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A18">
         <v>-3571.27624542796</v>
       </c>
@@ -1135,12 +1027,8 @@
       <c r="F18">
         <v>114.14111211733901</v>
       </c>
-      <c r="H18">
-        <f t="shared" si="0"/>
-        <v>5000.0000000000045</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A19">
         <v>-3512.1259451239398</v>
       </c>
@@ -1159,12 +1047,8 @@
       <c r="F19">
         <v>334.04822922503303</v>
       </c>
-      <c r="H19">
-        <f t="shared" si="0"/>
-        <v>1102.1814925754361</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A20">
         <v>-3511.5117116578299</v>
       </c>
@@ -1183,12 +1067,8 @@
       <c r="F20">
         <v>-351.238730327768</v>
       </c>
-      <c r="H20">
-        <f t="shared" si="0"/>
-        <v>5000.0000000000018</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A21">
         <v>-3146.96746839665</v>
       </c>
@@ -1207,12 +1087,8 @@
       <c r="F21">
         <v>-275.88259648410599</v>
       </c>
-      <c r="H21">
-        <f t="shared" si="0"/>
-        <v>3746.525577980492</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A22">
         <v>-3079.42375967721</v>
       </c>
@@ -1231,12 +1107,8 @@
       <c r="F22">
         <v>238.95842304296599</v>
       </c>
-      <c r="H22">
-        <f t="shared" si="0"/>
-        <v>2021.0259153867978</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A23">
         <v>-2678.9791162374399</v>
       </c>
@@ -1255,12 +1127,8 @@
       <c r="F23">
         <v>-199.91012786254899</v>
       </c>
-      <c r="H23">
-        <f t="shared" si="0"/>
-        <v>5000.0000000000082</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A24">
         <v>-2599.0859473331702</v>
       </c>
@@ -1279,12 +1147,8 @@
       <c r="F24">
         <v>500</v>
       </c>
-      <c r="H24">
-        <f t="shared" si="0"/>
-        <v>843.93783266021853</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A25">
         <v>-2129.21351112502</v>
       </c>
@@ -1303,12 +1167,8 @@
       <c r="F25">
         <v>-292.91925711707103</v>
       </c>
-      <c r="H25">
-        <f t="shared" si="0"/>
-        <v>3472.0125198155642</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A26">
         <v>-1977.25732408147</v>
       </c>
@@ -1327,12 +1187,8 @@
       <c r="F26">
         <v>-31.967402813133599</v>
       </c>
-      <c r="H26">
-        <f t="shared" si="0"/>
-        <v>5000</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A27">
         <v>-1838.5668945981199</v>
       </c>
@@ -1351,12 +1207,8 @@
       <c r="F27">
         <v>404.82732379311</v>
       </c>
-      <c r="H27">
-        <f t="shared" si="0"/>
-        <v>5000.0000000000045</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A28">
         <v>-1779.52317608205</v>
       </c>
@@ -1375,12 +1227,8 @@
       <c r="F28">
         <v>346.72625372303401</v>
       </c>
-      <c r="H28">
-        <f t="shared" si="0"/>
-        <v>5000.0000000000009</v>
-      </c>
-    </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A29">
         <v>-1767.0938703176</v>
       </c>
@@ -1399,12 +1247,8 @@
       <c r="F29">
         <v>193.399172285622</v>
       </c>
-      <c r="H29">
-        <f t="shared" si="0"/>
-        <v>4156.0621673397873</v>
-      </c>
-    </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A30">
         <v>-1537.93061123045</v>
       </c>
@@ -1423,12 +1267,8 @@
       <c r="F30">
         <v>500</v>
       </c>
-      <c r="H30">
-        <f t="shared" si="0"/>
-        <v>759.72498416084375</v>
-      </c>
-    </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A31">
         <v>-1028.3713146442001</v>
       </c>
@@ -1447,12 +1287,8 @@
       <c r="F31">
         <v>-206.847917144566</v>
       </c>
-      <c r="H31">
-        <f t="shared" si="0"/>
-        <v>4999.9999999999955</v>
-      </c>
-    </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A32">
         <v>-787.78110273104096</v>
       </c>
@@ -1471,12 +1307,8 @@
       <c r="F32">
         <v>-330.269786094952</v>
       </c>
-      <c r="H32">
-        <f t="shared" si="0"/>
-        <v>1272.9743794322424</v>
-      </c>
-    </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A33">
         <v>-568.82377416355303</v>
       </c>
@@ -1495,12 +1327,8 @@
       <c r="F33">
         <v>120.99847463154801</v>
       </c>
-      <c r="H33">
-        <f t="shared" si="0"/>
-        <v>5000.0000000000018</v>
-      </c>
-    </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A34">
         <v>-432.46954562565099</v>
       </c>
@@ -1519,12 +1347,8 @@
       <c r="F34">
         <v>411.79532327137099</v>
       </c>
-      <c r="H34">
-        <f t="shared" si="0"/>
-        <v>1064.8514837356204</v>
-      </c>
-    </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A35">
         <v>-134.813541478156</v>
       </c>
@@ -1543,12 +1367,8 @@
       <c r="F35">
         <v>39.424993001468103</v>
       </c>
-      <c r="H35">
-        <f t="shared" si="0"/>
-        <v>5000.0000000000036</v>
-      </c>
-    </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A36">
         <v>74.492303311346404</v>
       </c>
@@ -1567,12 +1387,8 @@
       <c r="F36">
         <v>260.705860635612</v>
       </c>
-      <c r="H36">
-        <f t="shared" si="0"/>
-        <v>4925.513101435421</v>
-      </c>
-    </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A37">
         <v>546.17566633093998</v>
       </c>
@@ -1591,12 +1407,8 @@
       <c r="F37">
         <v>-465.73230236790999</v>
       </c>
-      <c r="H37">
-        <f t="shared" si="0"/>
-        <v>1253.4744220195043</v>
-      </c>
-    </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A38">
         <v>621.58731078716903</v>
       </c>
@@ -1615,12 +1427,8 @@
       <c r="F38">
         <v>191.62204789453099</v>
       </c>
-      <c r="H38">
-        <f t="shared" si="0"/>
-        <v>3935.1485162643762</v>
-      </c>
-    </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A39">
         <v>1319.6720589460001</v>
       </c>
@@ -1639,12 +1447,8 @@
       <c r="F39">
         <v>-260.599387853466</v>
       </c>
-      <c r="H39">
-        <f t="shared" si="0"/>
-        <v>1527.9874801844335</v>
-      </c>
-    </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A40">
         <v>1570.02897422356</v>
       </c>
@@ -1663,12 +1467,8 @@
       <c r="F40">
         <v>138.87224003861601</v>
       </c>
-      <c r="H40">
-        <f t="shared" si="0"/>
-        <v>3443.5120303050126</v>
-      </c>
-    </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A41">
         <v>1879.3969729492501</v>
       </c>
@@ -1687,12 +1487,8 @@
       <c r="F41">
         <v>115.435676374726</v>
       </c>
-      <c r="H41">
-        <f t="shared" si="0"/>
-        <v>3125.3223103723944</v>
-      </c>
-    </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A42">
         <v>1890.0050389208</v>
       </c>
@@ -1711,12 +1507,8 @@
       <c r="F42">
         <v>98.506970161849793</v>
       </c>
-      <c r="H42">
-        <f t="shared" si="0"/>
-        <v>927.56174555182031</v>
-      </c>
-    </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A43">
         <v>2637.2097979401001</v>
       </c>
@@ -1735,12 +1527,8 @@
       <c r="F43">
         <v>-114.664350356616</v>
       </c>
-      <c r="H43">
-        <f t="shared" si="0"/>
-        <v>1338.5820528621841</v>
-      </c>
-    </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A44">
         <v>2677.8303635371699</v>
       </c>
@@ -1759,12 +1547,8 @@
       <c r="F44">
         <v>281.93189870277399</v>
       </c>
-      <c r="H44">
-        <f t="shared" si="0"/>
-        <v>2322.7361814113378</v>
-      </c>
-    </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A45">
         <v>2804.2389972381102</v>
       </c>
@@ -1783,12 +1567,8 @@
       <c r="F45">
         <v>218.69022752932699</v>
       </c>
-      <c r="H45">
-        <f t="shared" si="0"/>
-        <v>2227.7710098245329</v>
-      </c>
-    </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A46">
         <v>3061.45554268653</v>
       </c>
@@ -1807,12 +1587,8 @@
       <c r="F46">
         <v>-131.05704960564799</v>
       </c>
-      <c r="H46">
-        <f t="shared" si="0"/>
-        <v>1946.4264246338664</v>
-      </c>
-    </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A47">
         <v>3086.1409135599201</v>
       </c>
@@ -1831,12 +1607,8 @@
       <c r="F47">
         <v>-200.10393428968999</v>
       </c>
-      <c r="H47">
-        <f t="shared" si="0"/>
-        <v>1919.8772479556317</v>
-      </c>
-    </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A48">
         <v>3092.1344420728201</v>
       </c>
@@ -1855,12 +1627,8 @@
       <c r="F48">
         <v>-161.97477024831801</v>
       </c>
-      <c r="H48">
-        <f t="shared" si="0"/>
-        <v>1934.5129293238506</v>
-      </c>
-    </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A49">
         <v>3959.5982201086099</v>
       </c>
@@ -1879,12 +1647,8 @@
       <c r="F49">
         <v>-273.23245049488997</v>
       </c>
-      <c r="H49">
-        <f t="shared" si="0"/>
-        <v>1053.1422742228324</v>
-      </c>
-    </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A50">
         <v>3977.58135981847</v>
       </c>
@@ -1903,12 +1667,8 @@
       <c r="F50">
         <v>-248.900081210053</v>
       </c>
-      <c r="H50">
-        <f t="shared" si="0"/>
-        <v>1034.9180873207347</v>
-      </c>
-    </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A51">
         <v>4430.2932292044998</v>
       </c>
@@ -1926,10 +1686,6 @@
       </c>
       <c r="F51">
         <v>50.286199189568599</v>
-      </c>
-      <c r="H51">
-        <f t="shared" si="0"/>
-        <v>577.47395013975563</v>
       </c>
     </row>
   </sheetData>
@@ -1944,10 +1700,10 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9BAF61B8-1550-407A-8617-7412FDCBF564}">
-  <dimension ref="A1:H537"/>
+  <dimension ref="A1:F537"/>
   <sheetFormatPr defaultRowHeight="13.9" x14ac:dyDescent="0.4"/>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1959,7 +1715,7 @@
       <c r="E1" s="2"/>
       <c r="F1" s="2"/>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -1979,7 +1735,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A3">
         <v>-5000</v>
       </c>
@@ -1998,12 +1754,8 @@
       <c r="F3">
         <v>3967.3205736684799</v>
       </c>
-      <c r="H3">
-        <f>SQRT((D3-A3)^2+(E3-B3)^2+(F3-C3)^2)</f>
-        <v>4874.8071533601269</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A4">
         <v>-5000</v>
       </c>
@@ -2022,12 +1774,8 @@
       <c r="F4">
         <v>-3842.9826049898702</v>
       </c>
-      <c r="H4">
-        <f>SQRT((D4-A4)^2+(E4-B4)^2+(F4-C4)^2)</f>
-        <v>3536.5414371436791</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A5">
         <v>-5000</v>
       </c>
@@ -2046,12 +1794,8 @@
       <c r="F5">
         <v>-4884.9399383539303</v>
       </c>
-      <c r="H5">
-        <f t="shared" ref="H5:H68" si="0">SQRT((D5-A5)^2+(E5-B5)^2+(F5-C5)^2)</f>
-        <v>1779.0526369840729</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A6">
         <v>-5000</v>
       </c>
@@ -2070,12 +1814,8 @@
       <c r="F6">
         <v>692.56967233072396</v>
       </c>
-      <c r="H6">
-        <f t="shared" si="0"/>
-        <v>1478.0691391314886</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A7">
         <v>-5000</v>
       </c>
@@ -2094,12 +1834,8 @@
       <c r="F7">
         <v>-4015.9227303756302</v>
       </c>
-      <c r="H7">
-        <f t="shared" si="0"/>
-        <v>4422.7963219651356</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A8">
         <v>-5000</v>
       </c>
@@ -2118,12 +1854,8 @@
       <c r="F8">
         <v>2994.9653849132701</v>
       </c>
-      <c r="H8">
-        <f t="shared" si="0"/>
-        <v>3442.0924336494163</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A9">
         <v>-5000</v>
       </c>
@@ -2142,12 +1874,8 @@
       <c r="F9">
         <v>92.977604401646204</v>
       </c>
-      <c r="H9">
-        <f t="shared" si="0"/>
-        <v>2497.5982763783745</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A10">
         <v>-5000</v>
       </c>
@@ -2166,12 +1894,8 @@
       <c r="F10">
         <v>-2789.4345773667201</v>
       </c>
-      <c r="H10">
-        <f t="shared" si="0"/>
-        <v>2497.1282484913363</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A11">
         <v>-5000</v>
       </c>
@@ -2190,12 +1914,8 @@
       <c r="F11">
         <v>-2931.7338479077398</v>
       </c>
-      <c r="H11">
-        <f t="shared" si="0"/>
-        <v>2904.0107908790619</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A12">
         <v>-5000</v>
       </c>
@@ -2214,12 +1934,8 @@
       <c r="F12">
         <v>1520.79841217019</v>
       </c>
-      <c r="H12">
-        <f t="shared" si="0"/>
-        <v>4342.1812218787254</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A13">
         <v>-5000</v>
       </c>
@@ -2238,12 +1954,8 @@
       <c r="F13">
         <v>-1494.68012704236</v>
       </c>
-      <c r="H13">
-        <f t="shared" si="0"/>
-        <v>913.51510142766256</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A14">
         <v>-5000</v>
       </c>
@@ -2262,12 +1974,8 @@
       <c r="F14">
         <v>3699.0617456899499</v>
       </c>
-      <c r="H14">
-        <f t="shared" si="0"/>
-        <v>2060.3827403811342</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A15">
         <v>-5000</v>
       </c>
@@ -2286,12 +1994,8 @@
       <c r="F15">
         <v>2419.9443443537498</v>
       </c>
-      <c r="H15">
-        <f t="shared" si="0"/>
-        <v>4528.1591424743847</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A16">
         <v>-5000</v>
       </c>
@@ -2310,12 +2014,8 @@
       <c r="F16">
         <v>1135.3339965754201</v>
       </c>
-      <c r="H16">
-        <f t="shared" si="0"/>
-        <v>3509.9305790450471</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A17">
         <v>-5000</v>
       </c>
@@ -2334,12 +2034,8 @@
       <c r="F17">
         <v>-2002.0701272285601</v>
       </c>
-      <c r="H17">
-        <f t="shared" si="0"/>
-        <v>804.9025853004581</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A18">
         <v>-5000</v>
       </c>
@@ -2358,12 +2054,8 @@
       <c r="F18">
         <v>1835.0309218592499</v>
       </c>
-      <c r="H18">
-        <f t="shared" si="0"/>
-        <v>2497.8409446050641</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A19">
         <v>-5000</v>
       </c>
@@ -2382,12 +2074,8 @@
       <c r="F19">
         <v>3433.5382555718302</v>
       </c>
-      <c r="H19">
-        <f t="shared" si="0"/>
-        <v>981.38797626260805</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A20">
         <v>-5000</v>
       </c>
@@ -2406,12 +2094,8 @@
       <c r="F20">
         <v>-34.957672036401199</v>
       </c>
-      <c r="H20">
-        <f t="shared" si="0"/>
-        <v>1471.2231541958963</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A21">
         <v>-5000</v>
       </c>
@@ -2430,12 +2114,8 @@
       <c r="F21">
         <v>-3710.1073531563902</v>
       </c>
-      <c r="H21">
-        <f t="shared" si="0"/>
-        <v>882.41641567877662</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A22">
         <v>-5000</v>
       </c>
@@ -2454,12 +2134,8 @@
       <c r="F22">
         <v>2744.81331658726</v>
       </c>
-      <c r="H22">
-        <f t="shared" si="0"/>
-        <v>1840.460384963259</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A23">
         <v>-5000</v>
       </c>
@@ -2478,12 +2154,8 @@
       <c r="F23">
         <v>-937.53558078376204</v>
       </c>
-      <c r="H23">
-        <f t="shared" si="0"/>
-        <v>3191.740660501443</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A24">
         <v>-5000</v>
       </c>
@@ -2502,12 +2174,8 @@
       <c r="F24">
         <v>4080.1097010496001</v>
       </c>
-      <c r="H24">
-        <f t="shared" si="0"/>
-        <v>2765.2880618484069</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A25">
         <v>-5000</v>
       </c>
@@ -2526,12 +2194,8 @@
       <c r="F25">
         <v>-4024.4410244774199</v>
       </c>
-      <c r="H25">
-        <f t="shared" si="0"/>
-        <v>3450.0439600567543</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A26">
         <v>-5000</v>
       </c>
@@ -2550,12 +2214,8 @@
       <c r="F26">
         <v>269.99702624497098</v>
       </c>
-      <c r="H26">
-        <f t="shared" si="0"/>
-        <v>3815.52228969526</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A27">
         <v>-5000</v>
       </c>
@@ -2574,12 +2234,8 @@
       <c r="F27">
         <v>-220.00921295916399</v>
       </c>
-      <c r="H27">
-        <f t="shared" si="0"/>
-        <v>3665.68426682574</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A28">
         <v>-5000</v>
       </c>
@@ -2598,12 +2254,8 @@
       <c r="F28">
         <v>-909.34655029527505</v>
       </c>
-      <c r="H28">
-        <f t="shared" si="0"/>
-        <v>4474.3026179509361</v>
-      </c>
-    </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A29">
         <v>-5000</v>
       </c>
@@ -2622,12 +2274,8 @@
       <c r="F29">
         <v>-817.75230906151501</v>
       </c>
-      <c r="H29">
-        <f t="shared" si="0"/>
-        <v>2305.7742042118698</v>
-      </c>
-    </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A30">
         <v>-5000</v>
       </c>
@@ -2646,12 +2294,8 @@
       <c r="F30">
         <v>3821.6108012107302</v>
       </c>
-      <c r="H30">
-        <f t="shared" si="0"/>
-        <v>4036.5366439420955</v>
-      </c>
-    </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A31">
         <v>-5000</v>
       </c>
@@ -2670,12 +2314,8 @@
       <c r="F31">
         <v>3715.77168678109</v>
       </c>
-      <c r="H31">
-        <f t="shared" si="0"/>
-        <v>3711.5554274002566</v>
-      </c>
-    </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A32">
         <v>-5000</v>
       </c>
@@ -2694,12 +2334,8 @@
       <c r="F32">
         <v>-4369.5327343639201</v>
       </c>
-      <c r="H32">
-        <f t="shared" si="0"/>
-        <v>831.6354537618065</v>
-      </c>
-    </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A33">
         <v>-5000</v>
       </c>
@@ -2718,12 +2354,8 @@
       <c r="F33">
         <v>3386.9299034605701</v>
       </c>
-      <c r="H33">
-        <f t="shared" si="0"/>
-        <v>3277.8623350247472</v>
-      </c>
-    </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A34">
         <v>-5000</v>
       </c>
@@ -2742,12 +2374,8 @@
       <c r="F34">
         <v>2900.1022738075799</v>
       </c>
-      <c r="H34">
-        <f t="shared" si="0"/>
-        <v>3934.4697049236811</v>
-      </c>
-    </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A35">
         <v>-5000</v>
       </c>
@@ -2766,12 +2394,8 @@
       <c r="F35">
         <v>-2771.8260507752102</v>
       </c>
-      <c r="H35">
-        <f t="shared" si="0"/>
-        <v>3432.2559148160722</v>
-      </c>
-    </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A36">
         <v>-5000</v>
       </c>
@@ -2790,12 +2414,8 @@
       <c r="F36">
         <v>981.24394218134603</v>
       </c>
-      <c r="H36">
-        <f t="shared" si="0"/>
-        <v>3965.7249804704188</v>
-      </c>
-    </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A37">
         <v>-5000</v>
       </c>
@@ -2814,12 +2434,8 @@
       <c r="F37">
         <v>-675.74367161622604</v>
       </c>
-      <c r="H37">
-        <f t="shared" si="0"/>
-        <v>3102.4049691529685</v>
-      </c>
-    </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A38">
         <v>-5000</v>
       </c>
@@ -2838,12 +2454,8 @@
       <c r="F38">
         <v>-939.89490181865006</v>
       </c>
-      <c r="H38">
-        <f t="shared" si="0"/>
-        <v>4168.6599553050619</v>
-      </c>
-    </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A39">
         <v>-5000</v>
       </c>
@@ -2862,12 +2474,8 @@
       <c r="F39">
         <v>5000</v>
       </c>
-      <c r="H39">
-        <f t="shared" si="0"/>
-        <v>1075.0919356239763</v>
-      </c>
-    </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A40">
         <v>-5000</v>
       </c>
@@ -2886,12 +2494,8 @@
       <c r="F40">
         <v>2730.7981377372798</v>
       </c>
-      <c r="H40">
-        <f t="shared" si="0"/>
-        <v>561.71830481115251</v>
-      </c>
-    </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A41">
         <v>-5000</v>
       </c>
@@ -2910,12 +2514,8 @@
       <c r="F41">
         <v>5000</v>
       </c>
-      <c r="H41">
-        <f t="shared" si="0"/>
-        <v>811.02142350429972</v>
-      </c>
-    </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A42">
         <v>-5000</v>
       </c>
@@ -2934,12 +2534,8 @@
       <c r="F42">
         <v>4797.51561919305</v>
       </c>
-      <c r="H42">
-        <f t="shared" si="0"/>
-        <v>2217.8121965483033</v>
-      </c>
-    </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A43">
         <v>-5000</v>
       </c>
@@ -2958,12 +2554,8 @@
       <c r="F43">
         <v>-3300.6734947601299</v>
       </c>
-      <c r="H43">
-        <f t="shared" si="0"/>
-        <v>4193.5184684824244</v>
-      </c>
-    </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A44">
         <v>-5000</v>
       </c>
@@ -2982,12 +2574,8 @@
       <c r="F44">
         <v>-3919.3700872638501</v>
       </c>
-      <c r="H44">
-        <f t="shared" si="0"/>
-        <v>1222.5803393993835</v>
-      </c>
-    </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A45">
         <v>-5000</v>
       </c>
@@ -3006,12 +2594,8 @@
       <c r="F45">
         <v>-218.56181858924199</v>
       </c>
-      <c r="H45">
-        <f t="shared" si="0"/>
-        <v>1570.7107564586443</v>
-      </c>
-    </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A46">
         <v>-5000</v>
       </c>
@@ -3030,12 +2614,8 @@
       <c r="F46">
         <v>2601.0595102520301</v>
       </c>
-      <c r="H46">
-        <f t="shared" si="0"/>
-        <v>1001.7754394470295</v>
-      </c>
-    </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A47">
         <v>-5000</v>
       </c>
@@ -3054,12 +2634,8 @@
       <c r="F47">
         <v>-1950.4509907228801</v>
       </c>
-      <c r="H47">
-        <f t="shared" si="0"/>
-        <v>2719.6039063448707</v>
-      </c>
-    </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A48">
         <v>-5000</v>
       </c>
@@ -3078,12 +2654,8 @@
       <c r="F48">
         <v>1827.1476281330799</v>
       </c>
-      <c r="H48">
-        <f t="shared" si="0"/>
-        <v>1133.8748542010278</v>
-      </c>
-    </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A49">
         <v>-5000</v>
       </c>
@@ -3102,12 +2674,8 @@
       <c r="F49">
         <v>2440.27368559865</v>
       </c>
-      <c r="H49">
-        <f t="shared" si="0"/>
-        <v>1521.2992147504362</v>
-      </c>
-    </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A50">
         <v>-5000</v>
       </c>
@@ -3126,12 +2694,8 @@
       <c r="F50">
         <v>5000</v>
       </c>
-      <c r="H50">
-        <f t="shared" si="0"/>
-        <v>1869.0236159136484</v>
-      </c>
-    </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A51">
         <v>-5000</v>
       </c>
@@ -3150,12 +2714,8 @@
       <c r="F51">
         <v>-2157.8323977466498</v>
       </c>
-      <c r="H51">
-        <f t="shared" si="0"/>
-        <v>4990.2827805382312</v>
-      </c>
-    </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A52">
         <v>-5000</v>
       </c>
@@ -3174,12 +2734,8 @@
       <c r="F52">
         <v>3420.5520679923402</v>
       </c>
-      <c r="H52">
-        <f t="shared" si="0"/>
-        <v>3790.5117635141814</v>
-      </c>
-    </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A53">
         <v>-5000</v>
       </c>
@@ -3198,12 +2754,8 @@
       <c r="F53">
         <v>934.48004077863197</v>
       </c>
-      <c r="H53">
-        <f t="shared" si="0"/>
-        <v>1166.4689946717895</v>
-      </c>
-    </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A54">
         <v>-5000</v>
       </c>
@@ -3222,12 +2774,8 @@
       <c r="F54">
         <v>4513.2077385864104</v>
       </c>
-      <c r="H54">
-        <f t="shared" si="0"/>
-        <v>4658.0887611779626</v>
-      </c>
-    </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A55">
         <v>-5000</v>
       </c>
@@ -3246,12 +2794,8 @@
       <c r="F55">
         <v>-2354.2171860434401</v>
       </c>
-      <c r="H55">
-        <f t="shared" si="0"/>
-        <v>3360.0465203772746</v>
-      </c>
-    </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A56">
         <v>-5000</v>
       </c>
@@ -3270,12 +2814,8 @@
       <c r="F56">
         <v>-3300.8559677496901</v>
       </c>
-      <c r="H56">
-        <f t="shared" si="0"/>
-        <v>2350.5690666134938</v>
-      </c>
-    </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A57">
         <v>-5000</v>
       </c>
@@ -3294,12 +2834,8 @@
       <c r="F57">
         <v>-1705.40359744172</v>
       </c>
-      <c r="H57">
-        <f t="shared" si="0"/>
-        <v>3112.9454020522185</v>
-      </c>
-    </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A58">
         <v>-5000</v>
       </c>
@@ -3318,12 +2854,8 @@
       <c r="F58">
         <v>-5000</v>
       </c>
-      <c r="H58">
-        <f t="shared" si="0"/>
-        <v>527.67680031980092</v>
-      </c>
-    </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A59">
         <v>-5000</v>
       </c>
@@ -3342,12 +2874,8 @@
       <c r="F59">
         <v>1309.39443422368</v>
       </c>
-      <c r="H59">
-        <f t="shared" si="0"/>
-        <v>3858.5340030565999</v>
-      </c>
-    </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A60">
         <v>-5000</v>
       </c>
@@ -3366,12 +2894,8 @@
       <c r="F60">
         <v>-452.56445484416503</v>
       </c>
-      <c r="H60">
-        <f t="shared" si="0"/>
-        <v>1835.0289031984546</v>
-      </c>
-    </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A61">
         <v>-5000</v>
       </c>
@@ -3390,12 +2914,8 @@
       <c r="F61">
         <v>-1001.89852117701</v>
       </c>
-      <c r="H61">
-        <f t="shared" si="0"/>
-        <v>3851.4126671684735</v>
-      </c>
-    </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="62" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A62">
         <v>-5000</v>
       </c>
@@ -3414,12 +2934,8 @@
       <c r="F62">
         <v>-848.53042629262302</v>
       </c>
-      <c r="H62">
-        <f t="shared" si="0"/>
-        <v>3412.7178876246353</v>
-      </c>
-    </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="63" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A63">
         <v>-5000</v>
       </c>
@@ -3438,12 +2954,8 @@
       <c r="F63">
         <v>3260.2998284781202</v>
       </c>
-      <c r="H63">
-        <f t="shared" si="0"/>
-        <v>3968.8936698322318</v>
-      </c>
-    </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="64" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A64">
         <v>-5000</v>
       </c>
@@ -3462,12 +2974,8 @@
       <c r="F64">
         <v>1146.1008974026299</v>
       </c>
-      <c r="H64">
-        <f t="shared" si="0"/>
-        <v>2685.6760287580933</v>
-      </c>
-    </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="65" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A65">
         <v>-5000</v>
       </c>
@@ -3486,12 +2994,8 @@
       <c r="F65">
         <v>-3979.2148306661602</v>
       </c>
-      <c r="H65">
-        <f t="shared" si="0"/>
-        <v>4993.5375141376389</v>
-      </c>
-    </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="66" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A66">
         <v>-5000</v>
       </c>
@@ -3510,12 +3014,8 @@
       <c r="F66">
         <v>-3353.0577585593901</v>
       </c>
-      <c r="H66">
-        <f t="shared" si="0"/>
-        <v>4041.1373501089392</v>
-      </c>
-    </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="67" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A67">
         <v>-5000</v>
       </c>
@@ -3534,12 +3034,8 @@
       <c r="F67">
         <v>1117.71913924</v>
       </c>
-      <c r="H67">
-        <f t="shared" si="0"/>
-        <v>3350.0600666507207</v>
-      </c>
-    </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="68" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A68">
         <v>-5000</v>
       </c>
@@ -3558,12 +3054,8 @@
       <c r="F68">
         <v>2797.9436590557402</v>
       </c>
-      <c r="H68">
-        <f t="shared" si="0"/>
-        <v>1051.9335501859841</v>
-      </c>
-    </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="69" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A69">
         <v>-5000</v>
       </c>
@@ -3582,12 +3074,8 @@
       <c r="F69">
         <v>-1973.78722751036</v>
       </c>
-      <c r="H69">
-        <f t="shared" ref="H69:H132" si="1">SQRT((D69-A69)^2+(E69-B69)^2+(F69-C69)^2)</f>
-        <v>4794.6423530417696</v>
-      </c>
-    </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="70" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A70">
         <v>-5000</v>
       </c>
@@ -3606,12 +3094,8 @@
       <c r="F70">
         <v>378.317336970383</v>
       </c>
-      <c r="H70">
-        <f t="shared" si="1"/>
-        <v>4092.4903058783066</v>
-      </c>
-    </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="71" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A71">
         <v>-5000</v>
       </c>
@@ -3630,12 +3114,8 @@
       <c r="F71">
         <v>-827.154160731464</v>
       </c>
-      <c r="H71">
-        <f t="shared" si="1"/>
-        <v>703.65784162924206</v>
-      </c>
-    </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="72" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A72">
         <v>-5000</v>
       </c>
@@ -3654,12 +3134,8 @@
       <c r="F72">
         <v>4115.2969139787701</v>
       </c>
-      <c r="H72">
-        <f t="shared" si="1"/>
-        <v>3863.6457713094705</v>
-      </c>
-    </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="73" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A73">
         <v>-5000</v>
       </c>
@@ -3678,12 +3154,8 @@
       <c r="F73">
         <v>-1178.90185466049</v>
       </c>
-      <c r="H73">
-        <f t="shared" si="1"/>
-        <v>2881.4136880939436</v>
-      </c>
-    </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="74" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A74">
         <v>-5000</v>
       </c>
@@ -3702,12 +3174,8 @@
       <c r="F74">
         <v>-954.59302317634899</v>
       </c>
-      <c r="H74">
-        <f t="shared" si="1"/>
-        <v>3326.0530251501232</v>
-      </c>
-    </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="75" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A75">
         <v>-5000</v>
       </c>
@@ -3726,12 +3194,8 @@
       <c r="F75">
         <v>5000</v>
       </c>
-      <c r="H75">
-        <f t="shared" si="1"/>
-        <v>4593.5154849536566</v>
-      </c>
-    </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="76" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A76">
         <v>-5000</v>
       </c>
@@ -3750,12 +3214,8 @@
       <c r="F76">
         <v>-4544.8059189525902</v>
       </c>
-      <c r="H76">
-        <f t="shared" si="1"/>
-        <v>690.71102086648455</v>
-      </c>
-    </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="77" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A77">
         <v>-5000</v>
       </c>
@@ -3774,12 +3234,8 @@
       <c r="F77">
         <v>4313.9614353285997</v>
       </c>
-      <c r="H77">
-        <f t="shared" si="1"/>
-        <v>3725.7910866581533</v>
-      </c>
-    </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="78" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A78">
         <v>-5000</v>
       </c>
@@ -3798,12 +3254,8 @@
       <c r="F78">
         <v>-5000</v>
       </c>
-      <c r="H78">
-        <f t="shared" si="1"/>
-        <v>2952.0282455081092</v>
-      </c>
-    </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="79" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A79">
         <v>-5000</v>
       </c>
@@ -3822,12 +3274,8 @@
       <c r="F79">
         <v>233.88440924230301</v>
       </c>
-      <c r="H79">
-        <f t="shared" si="1"/>
-        <v>4320.6648652339209</v>
-      </c>
-    </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="80" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A80">
         <v>-5000</v>
       </c>
@@ -3846,12 +3294,8 @@
       <c r="F80">
         <v>3962.3812847071699</v>
       </c>
-      <c r="H80">
-        <f t="shared" si="1"/>
-        <v>919.40711650329854</v>
-      </c>
-    </row>
-    <row r="81" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="81" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A81">
         <v>-5000</v>
       </c>
@@ -3870,12 +3314,8 @@
       <c r="F81">
         <v>944.05688218258194</v>
       </c>
-      <c r="H81">
-        <f t="shared" si="1"/>
-        <v>3399.8577180403504</v>
-      </c>
-    </row>
-    <row r="82" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="82" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A82">
         <v>-5000</v>
       </c>
@@ -3894,12 +3334,8 @@
       <c r="F82">
         <v>2963.6904047953999</v>
       </c>
-      <c r="H82">
-        <f t="shared" si="1"/>
-        <v>771.30090926492903</v>
-      </c>
-    </row>
-    <row r="83" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="83" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A83">
         <v>-5000</v>
       </c>
@@ -3918,12 +3354,8 @@
       <c r="F83">
         <v>-4293.2516762909099</v>
       </c>
-      <c r="H83">
-        <f t="shared" si="1"/>
-        <v>1870.0005292357725</v>
-      </c>
-    </row>
-    <row r="84" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="84" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A84">
         <v>-5000</v>
       </c>
@@ -3942,12 +3374,8 @@
       <c r="F84">
         <v>-1992.4049725761899</v>
       </c>
-      <c r="H84">
-        <f t="shared" si="1"/>
-        <v>811.96724056501012</v>
-      </c>
-    </row>
-    <row r="85" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="85" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A85">
         <v>-5000</v>
       </c>
@@ -3966,12 +3394,8 @@
       <c r="F85">
         <v>-601.85170421471503</v>
       </c>
-      <c r="H85">
-        <f t="shared" si="1"/>
-        <v>2575.7752959588224</v>
-      </c>
-    </row>
-    <row r="86" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="86" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A86">
         <v>-5000</v>
       </c>
@@ -3990,12 +3414,8 @@
       <c r="F86">
         <v>-4962.6460908746503</v>
       </c>
-      <c r="H86">
-        <f t="shared" si="1"/>
-        <v>4088.7079839101739</v>
-      </c>
-    </row>
-    <row r="87" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="87" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A87">
         <v>-5000</v>
       </c>
@@ -4014,12 +3434,8 @@
       <c r="F87">
         <v>3540.8475512794198</v>
       </c>
-      <c r="H87">
-        <f t="shared" si="1"/>
-        <v>1668.3304045978007</v>
-      </c>
-    </row>
-    <row r="88" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="88" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A88">
         <v>-5000</v>
       </c>
@@ -4038,12 +3454,8 @@
       <c r="F88">
         <v>-1802.2370828923599</v>
       </c>
-      <c r="H88">
-        <f t="shared" si="1"/>
-        <v>3595.4769481903131</v>
-      </c>
-    </row>
-    <row r="89" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="89" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A89">
         <v>-5000</v>
       </c>
@@ -4062,12 +3474,8 @@
       <c r="F89">
         <v>174.56323270205701</v>
       </c>
-      <c r="H89">
-        <f t="shared" si="1"/>
-        <v>700.40316345804342</v>
-      </c>
-    </row>
-    <row r="90" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="90" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A90">
         <v>-5000</v>
       </c>
@@ -4086,12 +3494,8 @@
       <c r="F90">
         <v>-5000</v>
       </c>
-      <c r="H90">
-        <f t="shared" si="1"/>
-        <v>827.24901776454806</v>
-      </c>
-    </row>
-    <row r="91" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="91" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A91">
         <v>-5000</v>
       </c>
@@ -4110,12 +3514,8 @@
       <c r="F91">
         <v>-899.307553840379</v>
       </c>
-      <c r="H91">
-        <f t="shared" si="1"/>
-        <v>2066.891848974567</v>
-      </c>
-    </row>
-    <row r="92" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="92" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A92">
         <v>-5000</v>
       </c>
@@ -4134,12 +3534,8 @@
       <c r="F92">
         <v>4265.3790065838803</v>
       </c>
-      <c r="H92">
-        <f t="shared" si="1"/>
-        <v>1594.6788510406459</v>
-      </c>
-    </row>
-    <row r="93" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="93" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A93">
         <v>-5000</v>
       </c>
@@ -4158,12 +3554,8 @@
       <c r="F93">
         <v>3075.0006784888401</v>
       </c>
-      <c r="H93">
-        <f t="shared" si="1"/>
-        <v>661.25621811693452</v>
-      </c>
-    </row>
-    <row r="94" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="94" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A94">
         <v>-4995.9183893680502</v>
       </c>
@@ -4182,12 +3574,8 @@
       <c r="F94">
         <v>5000</v>
       </c>
-      <c r="H94">
-        <f t="shared" si="1"/>
-        <v>3800.254160170105</v>
-      </c>
-    </row>
-    <row r="95" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="95" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A95">
         <v>-4902.4688379486297</v>
       </c>
@@ -4206,12 +3594,8 @@
       <c r="F95">
         <v>710.29400532241903</v>
       </c>
-      <c r="H95">
-        <f t="shared" si="1"/>
-        <v>4999.9999999999982</v>
-      </c>
-    </row>
-    <row r="96" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="96" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A96">
         <v>-4897.9224016490998</v>
       </c>
@@ -4230,12 +3614,8 @@
       <c r="F96">
         <v>1839.76289779741</v>
       </c>
-      <c r="H96">
-        <f t="shared" si="1"/>
-        <v>4999.9999999999973</v>
-      </c>
-    </row>
-    <row r="97" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="97" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A97">
         <v>-4845.0807328338597</v>
       </c>
@@ -4254,12 +3634,8 @@
       <c r="F97">
         <v>222.98583670163799</v>
       </c>
-      <c r="H97">
-        <f t="shared" si="1"/>
-        <v>4999.9999999999991</v>
-      </c>
-    </row>
-    <row r="98" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="98" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A98">
         <v>-4833.38316603981</v>
       </c>
@@ -4278,12 +3654,8 @@
       <c r="F98">
         <v>-5000</v>
       </c>
-      <c r="H98">
-        <f t="shared" si="1"/>
-        <v>1531.4431755272144</v>
-      </c>
-    </row>
-    <row r="99" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="99" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A99">
         <v>-4801.8695969897499</v>
       </c>
@@ -4302,12 +3674,8 @@
       <c r="F99">
         <v>2531.3894455127302</v>
       </c>
-      <c r="H99">
-        <f t="shared" si="1"/>
-        <v>4999.9999999999991</v>
-      </c>
-    </row>
-    <row r="100" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="100" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A100">
         <v>-4779.7510965265701</v>
       </c>
@@ -4326,12 +3694,8 @@
       <c r="F100">
         <v>-3633.40422397159</v>
       </c>
-      <c r="H100">
-        <f t="shared" si="1"/>
-        <v>5000.0000000000045</v>
-      </c>
-    </row>
-    <row r="101" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="101" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A101">
         <v>-4778.6000056384901</v>
       </c>
@@ -4350,12 +3714,8 @@
       <c r="F101">
         <v>-1511.05478779547</v>
       </c>
-      <c r="H101">
-        <f t="shared" si="1"/>
-        <v>1302.2097711223462</v>
-      </c>
-    </row>
-    <row r="102" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="102" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A102">
         <v>-4745.5395343539703</v>
       </c>
@@ -4374,12 +3734,8 @@
       <c r="F102">
         <v>-1131.3133659974301</v>
       </c>
-      <c r="H102">
-        <f t="shared" si="1"/>
-        <v>4999.9999999999945</v>
-      </c>
-    </row>
-    <row r="103" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="103" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A103">
         <v>-4741.1935678637801</v>
       </c>
@@ -4398,12 +3754,8 @@
       <c r="F103">
         <v>1654.8249163282901</v>
       </c>
-      <c r="H103">
-        <f t="shared" si="1"/>
-        <v>4999.9999999999982</v>
-      </c>
-    </row>
-    <row r="104" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="104" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A104">
         <v>-4737.9316880512397</v>
       </c>
@@ -4422,12 +3774,8 @@
       <c r="F104">
         <v>3732.5209214589399</v>
       </c>
-      <c r="H104">
-        <f t="shared" si="1"/>
-        <v>1190.1502150790241</v>
-      </c>
-    </row>
-    <row r="105" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="105" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A105">
         <v>-4677.0652761731099</v>
       </c>
@@ -4446,12 +3794,8 @@
       <c r="F105">
         <v>-734.70625522115404</v>
       </c>
-      <c r="H105">
-        <f t="shared" si="1"/>
-        <v>5000</v>
-      </c>
-    </row>
-    <row r="106" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="106" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A106">
         <v>-4668.2554261217701</v>
       </c>
@@ -4470,12 +3814,8 @@
       <c r="F106">
         <v>-1891.8270613837799</v>
       </c>
-      <c r="H106">
-        <f t="shared" si="1"/>
-        <v>3905.2282724875818</v>
-      </c>
-    </row>
-    <row r="107" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="107" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A107">
         <v>-4645.0629824069101</v>
       </c>
@@ -4494,12 +3834,8 @@
       <c r="F107">
         <v>-5000</v>
       </c>
-      <c r="H107">
-        <f t="shared" si="1"/>
-        <v>2910.808895688092</v>
-      </c>
-    </row>
-    <row r="108" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="108" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A108">
         <v>-4642.4593783669197</v>
       </c>
@@ -4518,12 +3854,8 @@
       <c r="F108">
         <v>-156.270705047679</v>
       </c>
-      <c r="H108">
-        <f t="shared" si="1"/>
-        <v>4999.9999999999973</v>
-      </c>
-    </row>
-    <row r="109" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="109" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A109">
         <v>-4628.9350051449201</v>
       </c>
@@ -4542,12 +3874,8 @@
       <c r="F109">
         <v>-3852.5531866882502</v>
       </c>
-      <c r="H109">
-        <f t="shared" si="1"/>
-        <v>5000</v>
-      </c>
-    </row>
-    <row r="110" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="110" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A110">
         <v>-4571.8412893391896</v>
       </c>
@@ -4566,12 +3894,8 @@
       <c r="F110">
         <v>4017.0837988047901</v>
       </c>
-      <c r="H110">
-        <f t="shared" si="1"/>
-        <v>4999.9999999999964</v>
-      </c>
-    </row>
-    <row r="111" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="111" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A111">
         <v>-4565.7579265067598</v>
       </c>
@@ -4590,12 +3914,8 @@
       <c r="F111">
         <v>2206.3490219843502</v>
       </c>
-      <c r="H111">
-        <f t="shared" si="1"/>
-        <v>4814.484257451858</v>
-      </c>
-    </row>
-    <row r="112" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="112" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A112">
         <v>-4554.8229305432296</v>
       </c>
@@ -4614,12 +3934,8 @@
       <c r="F112">
         <v>4432.9170037861904</v>
       </c>
-      <c r="H112">
-        <f t="shared" si="1"/>
-        <v>1080.1204359450621</v>
-      </c>
-    </row>
-    <row r="113" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="113" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A113">
         <v>-4537.5594453207796</v>
       </c>
@@ -4638,12 +3954,8 @@
       <c r="F113">
         <v>-1652.84041139802</v>
       </c>
-      <c r="H113">
-        <f t="shared" si="1"/>
-        <v>5000.0000000000018</v>
-      </c>
-    </row>
-    <row r="114" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="114" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A114">
         <v>-4531.8772066246602</v>
       </c>
@@ -4662,12 +3974,8 @@
       <c r="F114">
         <v>-5000</v>
       </c>
-      <c r="H114">
-        <f t="shared" si="1"/>
-        <v>705.21262396700899</v>
-      </c>
-    </row>
-    <row r="115" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="115" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A115">
         <v>-4518.7611476125003</v>
       </c>
@@ -4686,12 +3994,8 @@
       <c r="F115">
         <v>3043.1147951459102</v>
       </c>
-      <c r="H115">
-        <f t="shared" si="1"/>
-        <v>5000.0000000000036</v>
-      </c>
-    </row>
-    <row r="116" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="116" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A116">
         <v>-4464.3136579720203</v>
       </c>
@@ -4710,12 +4014,8 @@
       <c r="F116">
         <v>2077.7692845931201</v>
       </c>
-      <c r="H116">
-        <f t="shared" si="1"/>
-        <v>5000.0000000000082</v>
-      </c>
-    </row>
-    <row r="117" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="117" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A117">
         <v>-4463.6873537913898</v>
       </c>
@@ -4734,12 +4034,8 @@
       <c r="F117">
         <v>-3104.5190541469901</v>
       </c>
-      <c r="H117">
-        <f t="shared" si="1"/>
-        <v>5000.0000000000045</v>
-      </c>
-    </row>
-    <row r="118" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="118" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A118">
         <v>-4437.4249103749999</v>
       </c>
@@ -4758,12 +4054,8 @@
       <c r="F118">
         <v>2387.1780213112302</v>
       </c>
-      <c r="H118">
-        <f t="shared" si="1"/>
-        <v>4999.9999999999964</v>
-      </c>
-    </row>
-    <row r="119" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="119" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A119">
         <v>-4422.2895072511801</v>
       </c>
@@ -4782,12 +4074,8 @@
       <c r="F119">
         <v>1034.2941841404299</v>
       </c>
-      <c r="H119">
-        <f t="shared" si="1"/>
-        <v>5000.0000000000018</v>
-      </c>
-    </row>
-    <row r="120" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="120" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A120">
         <v>-4410.2825974755297</v>
       </c>
@@ -4806,12 +4094,8 @@
       <c r="F120">
         <v>-3320.9551037198898</v>
       </c>
-      <c r="H120">
-        <f t="shared" si="1"/>
-        <v>4833.7867686378049</v>
-      </c>
-    </row>
-    <row r="121" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="121" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A121">
         <v>-4403.6072775562398</v>
       </c>
@@ -4830,12 +4114,8 @@
       <c r="F121">
         <v>-2833.9787801436501</v>
       </c>
-      <c r="H121">
-        <f t="shared" si="1"/>
-        <v>5000.0000000000055</v>
-      </c>
-    </row>
-    <row r="122" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="122" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A122">
         <v>-4397.2949363110101</v>
       </c>
@@ -4854,12 +4134,8 @@
       <c r="F122">
         <v>344.00389092010801</v>
       </c>
-      <c r="H122">
-        <f t="shared" si="1"/>
-        <v>4999.9999999999955</v>
-      </c>
-    </row>
-    <row r="123" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="123" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A123">
         <v>-4383.6907791511803</v>
       </c>
@@ -4878,12 +4154,8 @@
       <c r="F123">
         <v>2800.4246200828902</v>
       </c>
-      <c r="H123">
-        <f t="shared" si="1"/>
-        <v>3468.5568244727824</v>
-      </c>
-    </row>
-    <row r="124" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="124" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A124">
         <v>-4367.7281296958299</v>
       </c>
@@ -4902,12 +4174,8 @@
       <c r="F124">
         <v>1068.7084410836001</v>
       </c>
-      <c r="H124">
-        <f t="shared" si="1"/>
-        <v>5000.0000000000018</v>
-      </c>
-    </row>
-    <row r="125" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="125" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A125">
         <v>-4366.8874821392701</v>
       </c>
@@ -4926,12 +4194,8 @@
       <c r="F125">
         <v>-4411.1228386120501</v>
       </c>
-      <c r="H125">
-        <f t="shared" si="1"/>
-        <v>2099.3712794734183</v>
-      </c>
-    </row>
-    <row r="126" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="126" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A126">
         <v>-4364.3405761473996</v>
       </c>
@@ -4950,12 +4214,8 @@
       <c r="F126">
         <v>3990.2109783027499</v>
       </c>
-      <c r="H126">
-        <f t="shared" si="1"/>
-        <v>3722.627382779332</v>
-      </c>
-    </row>
-    <row r="127" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="127" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A127">
         <v>-4326.70685705914</v>
       </c>
@@ -4974,12 +4234,8 @@
       <c r="F127">
         <v>-3689.8541014591601</v>
       </c>
-      <c r="H127">
-        <f t="shared" si="1"/>
-        <v>5000.0000000000027</v>
-      </c>
-    </row>
-    <row r="128" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="128" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A128">
         <v>-4325.9353452297401</v>
       </c>
@@ -4998,12 +4254,8 @@
       <c r="F128">
         <v>52.479561930654803</v>
       </c>
-      <c r="H128">
-        <f t="shared" si="1"/>
-        <v>5000.0000000000045</v>
-      </c>
-    </row>
-    <row r="129" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="129" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A129">
         <v>-4314.4944258736896</v>
       </c>
@@ -5022,12 +4274,8 @@
       <c r="F129">
         <v>1355.7031235774</v>
       </c>
-      <c r="H129">
-        <f t="shared" si="1"/>
-        <v>2212.2905692253134</v>
-      </c>
-    </row>
-    <row r="130" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="130" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A130">
         <v>-4313.76832575146</v>
       </c>
@@ -5046,12 +4294,8 @@
       <c r="F130">
         <v>4264.6343999950304</v>
       </c>
-      <c r="H130">
-        <f t="shared" si="1"/>
-        <v>5000</v>
-      </c>
-    </row>
-    <row r="131" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="131" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A131">
         <v>-4310.4184902340903</v>
       </c>
@@ -5070,12 +4314,8 @@
       <c r="F131">
         <v>-5000</v>
       </c>
-      <c r="H131">
-        <f t="shared" si="1"/>
-        <v>712.47386330372876</v>
-      </c>
-    </row>
-    <row r="132" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="132" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A132">
         <v>-4291.2543332252999</v>
       </c>
@@ -5094,12 +4334,8 @@
       <c r="F132">
         <v>3191.43622332523</v>
       </c>
-      <c r="H132">
-        <f t="shared" si="1"/>
-        <v>2188.154857222853</v>
-      </c>
-    </row>
-    <row r="133" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="133" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A133">
         <v>-4283.6534423160701</v>
       </c>
@@ -5118,12 +4354,8 @@
       <c r="F133">
         <v>2025.8333289903201</v>
       </c>
-      <c r="H133">
-        <f t="shared" ref="H133:H196" si="2">SQRT((D133-A133)^2+(E133-B133)^2+(F133-C133)^2)</f>
-        <v>5000.0000000000018</v>
-      </c>
-    </row>
-    <row r="134" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="134" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A134">
         <v>-4275.03899601177</v>
       </c>
@@ -5142,12 +4374,8 @@
       <c r="F134">
         <v>1719.6657821466599</v>
       </c>
-      <c r="H134">
-        <f t="shared" si="2"/>
-        <v>4294.7873760329803</v>
-      </c>
-    </row>
-    <row r="135" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="135" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A135">
         <v>-4262.2094097217496</v>
       </c>
@@ -5166,12 +4394,8 @@
       <c r="F135">
         <v>-3886.8719212005999</v>
       </c>
-      <c r="H135">
-        <f t="shared" si="2"/>
-        <v>3580.1942724405749</v>
-      </c>
-    </row>
-    <row r="136" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="136" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A136">
         <v>-4250.3490652680703</v>
       </c>
@@ -5190,12 +4414,8 @@
       <c r="F136">
         <v>4149.1948241501304</v>
       </c>
-      <c r="H136">
-        <f t="shared" si="2"/>
-        <v>2651.7178861461794</v>
-      </c>
-    </row>
-    <row r="137" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="137" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A137">
         <v>-4242.6329320709701</v>
       </c>
@@ -5214,12 +4434,8 @@
       <c r="F137">
         <v>-2739.2351317057701</v>
       </c>
-      <c r="H137">
-        <f t="shared" si="2"/>
-        <v>1094.7717275124148</v>
-      </c>
-    </row>
-    <row r="138" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="138" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A138">
         <v>-4224.8790461629796</v>
       </c>
@@ -5238,12 +4454,8 @@
       <c r="F138">
         <v>2230.6370517021701</v>
       </c>
-      <c r="H138">
-        <f t="shared" si="2"/>
-        <v>5000.0000000000045</v>
-      </c>
-    </row>
-    <row r="139" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="139" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A139">
         <v>-4223.0760031504296</v>
       </c>
@@ -5262,12 +4474,8 @@
       <c r="F139">
         <v>3323.88078191874</v>
       </c>
-      <c r="H139">
-        <f t="shared" si="2"/>
-        <v>5000.0000000000027</v>
-      </c>
-    </row>
-    <row r="140" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="140" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A140">
         <v>-4210.6959543031999</v>
       </c>
@@ -5286,12 +4494,8 @@
       <c r="F140">
         <v>-5000</v>
       </c>
-      <c r="H140">
-        <f t="shared" si="2"/>
-        <v>4297.1199140883682</v>
-      </c>
-    </row>
-    <row r="141" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="141" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A141">
         <v>-4149.9587486404298</v>
       </c>
@@ -5310,12 +4514,8 @@
       <c r="F141">
         <v>-4693.7449761498701</v>
       </c>
-      <c r="H141">
-        <f t="shared" si="2"/>
-        <v>1038.9332100650729</v>
-      </c>
-    </row>
-    <row r="142" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="142" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A142">
         <v>-4139.8398731768102</v>
       </c>
@@ -5334,12 +4534,8 @@
       <c r="F142">
         <v>-3980.0235673730999</v>
       </c>
-      <c r="H142">
-        <f t="shared" si="2"/>
-        <v>1199.7458398298907</v>
-      </c>
-    </row>
-    <row r="143" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="143" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A143">
         <v>-4102.31621428781</v>
       </c>
@@ -5358,12 +4554,8 @@
       <c r="F143">
         <v>-2378.61716378044</v>
       </c>
-      <c r="H143">
-        <f t="shared" si="2"/>
-        <v>5000.0000000000036</v>
-      </c>
-    </row>
-    <row r="144" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="144" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A144">
         <v>-4085.87573408055</v>
       </c>
@@ -5382,12 +4574,8 @@
       <c r="F144">
         <v>-4238.4511681951599</v>
       </c>
-      <c r="H144">
-        <f t="shared" si="2"/>
-        <v>1487.5537018742179</v>
-      </c>
-    </row>
-    <row r="145" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="145" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A145">
         <v>-4052.3417348408102</v>
       </c>
@@ -5406,12 +4594,8 @@
       <c r="F145">
         <v>2552.1831647775698</v>
       </c>
-      <c r="H145">
-        <f t="shared" si="2"/>
-        <v>2787.7094307746806</v>
-      </c>
-    </row>
-    <row r="146" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="146" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A146">
         <v>-4012.3927099831799</v>
       </c>
@@ -5430,12 +4614,8 @@
       <c r="F146">
         <v>1441.21942142996</v>
       </c>
-      <c r="H146">
-        <f t="shared" si="2"/>
-        <v>5000</v>
-      </c>
-    </row>
-    <row r="147" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="147" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A147">
         <v>-3949.0185782799099</v>
       </c>
@@ -5454,12 +4634,8 @@
       <c r="F147">
         <v>-5000</v>
       </c>
-      <c r="H147">
-        <f t="shared" si="2"/>
-        <v>1225.2684146655433</v>
-      </c>
-    </row>
-    <row r="148" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="148" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A148">
         <v>-3946.6972050416398</v>
       </c>
@@ -5478,12 +4654,8 @@
       <c r="F148">
         <v>4666.8774301822696</v>
       </c>
-      <c r="H148">
-        <f t="shared" si="2"/>
-        <v>1759.8419278626147</v>
-      </c>
-    </row>
-    <row r="149" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="149" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A149">
         <v>-3941.6219178265901</v>
       </c>
@@ -5502,12 +4674,8 @@
       <c r="F149">
         <v>5000</v>
       </c>
-      <c r="H149">
-        <f t="shared" si="2"/>
-        <v>4332.5114939530813</v>
-      </c>
-    </row>
-    <row r="150" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="150" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A150">
         <v>-3936.7418939639501</v>
       </c>
@@ -5526,12 +4694,8 @@
       <c r="F150">
         <v>3841.4587150244702</v>
       </c>
-      <c r="H150">
-        <f t="shared" si="2"/>
-        <v>4804.0054216982862</v>
-      </c>
-    </row>
-    <row r="151" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="151" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A151">
         <v>-3935.6695028662102</v>
       </c>
@@ -5550,12 +4714,8 @@
       <c r="F151">
         <v>4946.1711561580796</v>
       </c>
-      <c r="H151">
-        <f t="shared" si="2"/>
-        <v>4999.9999999999955</v>
-      </c>
-    </row>
-    <row r="152" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="152" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A152">
         <v>-3927.6312383751701</v>
       </c>
@@ -5574,12 +4734,8 @@
       <c r="F152">
         <v>3077.3782499061699</v>
       </c>
-      <c r="H152">
-        <f t="shared" si="2"/>
-        <v>2116.5642348157139</v>
-      </c>
-    </row>
-    <row r="153" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="153" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A153">
         <v>-3902.8957277388399</v>
       </c>
@@ -5598,12 +4754,8 @@
       <c r="F153">
         <v>980.91313870055001</v>
       </c>
-      <c r="H153">
-        <f t="shared" si="2"/>
-        <v>4999.9999999999982</v>
-      </c>
-    </row>
-    <row r="154" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="154" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A154">
         <v>-3868.1224774494099</v>
       </c>
@@ -5622,12 +4774,8 @@
       <c r="F154">
         <v>1259.87007037014</v>
       </c>
-      <c r="H154">
-        <f t="shared" si="2"/>
-        <v>4015.6602716941602</v>
-      </c>
-    </row>
-    <row r="155" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="155" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A155">
         <v>-3831.2198551605902</v>
       </c>
@@ -5646,12 +4794,8 @@
       <c r="F155">
         <v>1968.08629923084</v>
       </c>
-      <c r="H155">
-        <f t="shared" si="2"/>
-        <v>1820.9628639113146</v>
-      </c>
-    </row>
-    <row r="156" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="156" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A156">
         <v>-3786.8157407826702</v>
       </c>
@@ -5670,12 +4814,8 @@
       <c r="F156">
         <v>-1593.8102394211201</v>
       </c>
-      <c r="H156">
-        <f t="shared" si="2"/>
-        <v>5000.0000000000027</v>
-      </c>
-    </row>
-    <row r="157" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="157" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A157">
         <v>-3779.5870632398301</v>
       </c>
@@ -5694,12 +4834,8 @@
       <c r="F157">
         <v>1498.4528085801001</v>
       </c>
-      <c r="H157">
-        <f t="shared" si="2"/>
-        <v>5000.0000000000036</v>
-      </c>
-    </row>
-    <row r="158" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="158" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A158">
         <v>-3767.5379162457498</v>
       </c>
@@ -5718,12 +4854,8 @@
       <c r="F158">
         <v>5000</v>
       </c>
-      <c r="H158">
-        <f t="shared" si="2"/>
-        <v>3936.0620296923225</v>
-      </c>
-    </row>
-    <row r="159" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="159" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A159">
         <v>-3736.6974383588499</v>
       </c>
@@ -5742,12 +4874,8 @@
       <c r="F159">
         <v>4217.2742776409204</v>
       </c>
-      <c r="H159">
-        <f t="shared" si="2"/>
-        <v>5000.0000000000027</v>
-      </c>
-    </row>
-    <row r="160" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="160" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A160">
         <v>-3655.8679416105301</v>
       </c>
@@ -5766,12 +4894,8 @@
       <c r="F160">
         <v>2664.2059618148101</v>
       </c>
-      <c r="H160">
-        <f t="shared" si="2"/>
-        <v>4634.6864651689948</v>
-      </c>
-    </row>
-    <row r="161" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="161" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A161">
         <v>-3634.45936732771</v>
       </c>
@@ -5790,12 +4914,8 @@
       <c r="F161">
         <v>4187.8639575252801</v>
       </c>
-      <c r="H161">
-        <f t="shared" si="2"/>
-        <v>4564.2211869673492</v>
-      </c>
-    </row>
-    <row r="162" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="162" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A162">
         <v>-3628.8074308067999</v>
       </c>
@@ -5814,12 +4934,8 @@
       <c r="F162">
         <v>1765.7862791524201</v>
       </c>
-      <c r="H162">
-        <f t="shared" si="2"/>
-        <v>5000.0000000000018</v>
-      </c>
-    </row>
-    <row r="163" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="163" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A163">
         <v>-3558.93159825572</v>
       </c>
@@ -5838,12 +4954,8 @@
       <c r="F163">
         <v>2701.62965415288</v>
       </c>
-      <c r="H163">
-        <f t="shared" si="2"/>
-        <v>4997.3893127542697</v>
-      </c>
-    </row>
-    <row r="164" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="164" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A164">
         <v>-3543.1880048665498</v>
       </c>
@@ -5862,12 +4974,8 @@
       <c r="F164">
         <v>3717.6954852355102</v>
       </c>
-      <c r="H164">
-        <f t="shared" si="2"/>
-        <v>3179.0371360886902</v>
-      </c>
-    </row>
-    <row r="165" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="165" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A165">
         <v>-3496.5400703391701</v>
       </c>
@@ -5886,12 +4994,8 @@
       <c r="F165">
         <v>314.90895680908397</v>
       </c>
-      <c r="H165">
-        <f t="shared" si="2"/>
-        <v>2193.4348902227284</v>
-      </c>
-    </row>
-    <row r="166" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="166" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A166">
         <v>-3496.37091092846</v>
       </c>
@@ -5910,12 +5014,8 @@
       <c r="F166">
         <v>3088.0524863426899</v>
       </c>
-      <c r="H166">
-        <f t="shared" si="2"/>
-        <v>4999.9999999999964</v>
-      </c>
-    </row>
-    <row r="167" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="167" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A167">
         <v>-3482.77574037465</v>
       </c>
@@ -5934,12 +5034,8 @@
       <c r="F167">
         <v>5000</v>
       </c>
-      <c r="H167">
-        <f t="shared" si="2"/>
-        <v>1714.283084210331</v>
-      </c>
-    </row>
-    <row r="168" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="168" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A168">
         <v>-3457.8316756064801</v>
       </c>
@@ -5958,12 +5054,8 @@
       <c r="F168">
         <v>1744.7141653925601</v>
       </c>
-      <c r="H168">
-        <f t="shared" si="2"/>
-        <v>3983.3918629955601</v>
-      </c>
-    </row>
-    <row r="169" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="169" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A169">
         <v>-3453.7495830051998</v>
       </c>
@@ -5982,12 +5074,8 @@
       <c r="F169">
         <v>5000</v>
       </c>
-      <c r="H169">
-        <f t="shared" si="2"/>
-        <v>559.22306424772296</v>
-      </c>
-    </row>
-    <row r="170" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="170" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A170">
         <v>-3418.2901461992901</v>
       </c>
@@ -6006,12 +5094,8 @@
       <c r="F170">
         <v>3561.56028795574</v>
       </c>
-      <c r="H170">
-        <f t="shared" si="2"/>
-        <v>4532.1568212290003</v>
-      </c>
-    </row>
-    <row r="171" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="171" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A171">
         <v>-3411.1009529785501</v>
       </c>
@@ -6030,12 +5114,8 @@
       <c r="F171">
         <v>-4366.62477861562</v>
       </c>
-      <c r="H171">
-        <f t="shared" si="2"/>
-        <v>1207.7638410721072</v>
-      </c>
-    </row>
-    <row r="172" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="172" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A172">
         <v>-3381.9435226359701</v>
       </c>
@@ -6054,12 +5134,8 @@
       <c r="F172">
         <v>-3987.6763025478799</v>
       </c>
-      <c r="H172">
-        <f t="shared" si="2"/>
-        <v>4999.9999999999918</v>
-      </c>
-    </row>
-    <row r="173" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="173" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A173">
         <v>-3381.4896791843498</v>
       </c>
@@ -6078,12 +5154,8 @@
       <c r="F173">
         <v>2405.8381145101198</v>
       </c>
-      <c r="H173">
-        <f t="shared" si="2"/>
-        <v>4999.9999999999927</v>
-      </c>
-    </row>
-    <row r="174" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="174" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A174">
         <v>-3365.5420130995199</v>
       </c>
@@ -6102,12 +5174,8 @@
       <c r="F174">
         <v>-2574.3158992690001</v>
       </c>
-      <c r="H174">
-        <f t="shared" si="2"/>
-        <v>4999.9999999999991</v>
-      </c>
-    </row>
-    <row r="175" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="175" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A175">
         <v>-3353.52228170234</v>
       </c>
@@ -6126,12 +5194,8 @@
       <c r="F175">
         <v>2234.8919562021902</v>
       </c>
-      <c r="H175">
-        <f t="shared" si="2"/>
-        <v>3774.7315853344585</v>
-      </c>
-    </row>
-    <row r="176" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="176" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A176">
         <v>-3353.1205822203501</v>
       </c>
@@ -6150,12 +5214,8 @@
       <c r="F176">
         <v>5000</v>
       </c>
-      <c r="H176">
-        <f t="shared" si="2"/>
-        <v>2292.6491828148223</v>
-      </c>
-    </row>
-    <row r="177" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="177" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A177">
         <v>-3330.9768393029899</v>
       </c>
@@ -6174,12 +5234,8 @@
       <c r="F177">
         <v>-1556.16456585125</v>
       </c>
-      <c r="H177">
-        <f t="shared" si="2"/>
-        <v>5000.0000000000018</v>
-      </c>
-    </row>
-    <row r="178" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="178" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A178">
         <v>-3286.85924593133</v>
       </c>
@@ -6198,12 +5254,8 @@
       <c r="F178">
         <v>-975.14499275468097</v>
       </c>
-      <c r="H178">
-        <f t="shared" si="2"/>
-        <v>5000.0000000000009</v>
-      </c>
-    </row>
-    <row r="179" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="179" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A179">
         <v>-3252.7636253688802</v>
       </c>
@@ -6222,12 +5274,8 @@
       <c r="F179">
         <v>5000</v>
       </c>
-      <c r="H179">
-        <f t="shared" si="2"/>
-        <v>4323.1944520813076</v>
-      </c>
-    </row>
-    <row r="180" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="180" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A180">
         <v>-3193.2896219546901</v>
       </c>
@@ -6246,12 +5294,8 @@
       <c r="F180">
         <v>3871.94801863882</v>
       </c>
-      <c r="H180">
-        <f t="shared" si="2"/>
-        <v>2584.5631027991594</v>
-      </c>
-    </row>
-    <row r="181" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="181" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A181">
         <v>-3183.76253826938</v>
       </c>
@@ -6270,12 +5314,8 @@
       <c r="F181">
         <v>-1738.5757099134801</v>
       </c>
-      <c r="H181">
-        <f t="shared" si="2"/>
-        <v>4440.776935752283</v>
-      </c>
-    </row>
-    <row r="182" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="182" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A182">
         <v>-3132.5588682590901</v>
       </c>
@@ -6294,12 +5334,8 @@
       <c r="F182">
         <v>3911.76974298091</v>
       </c>
-      <c r="H182">
-        <f t="shared" si="2"/>
-        <v>5000.0000000000018</v>
-      </c>
-    </row>
-    <row r="183" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="183" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A183">
         <v>-3127.0367261656902</v>
       </c>
@@ -6318,12 +5354,8 @@
       <c r="F183">
         <v>2596.4402036773399</v>
       </c>
-      <c r="H183">
-        <f t="shared" si="2"/>
-        <v>4999.9999999999982</v>
-      </c>
-    </row>
-    <row r="184" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="184" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A184">
         <v>-3118.6636298569401</v>
       </c>
@@ -6342,12 +5374,8 @@
       <c r="F184">
         <v>114.81785932774901</v>
       </c>
-      <c r="H184">
-        <f t="shared" si="2"/>
-        <v>2301.1650233282439</v>
-      </c>
-    </row>
-    <row r="185" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="185" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A185">
         <v>-3115.7239937971999</v>
       </c>
@@ -6366,12 +5394,8 @@
       <c r="F185">
         <v>-1287.3234763738401</v>
       </c>
-      <c r="H185">
-        <f t="shared" si="2"/>
-        <v>5000.0000000000045</v>
-      </c>
-    </row>
-    <row r="186" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="186" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A186">
         <v>-3093.6809716133298</v>
       </c>
@@ -6390,12 +5414,8 @@
       <c r="F186">
         <v>2533.9914846233601</v>
       </c>
-      <c r="H186">
-        <f t="shared" si="2"/>
-        <v>4999.9999999999945</v>
-      </c>
-    </row>
-    <row r="187" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="187" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A187">
         <v>-3089.6730849926598</v>
       </c>
@@ -6414,12 +5434,8 @@
       <c r="F187">
         <v>-5000</v>
       </c>
-      <c r="H187">
-        <f t="shared" si="2"/>
-        <v>1507.0880569306512</v>
-      </c>
-    </row>
-    <row r="188" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="188" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A188">
         <v>-3084.8236285046701</v>
       </c>
@@ -6438,12 +5454,8 @@
       <c r="F188">
         <v>3807.3297073071199</v>
       </c>
-      <c r="H188">
-        <f t="shared" si="2"/>
-        <v>5000.0000000000009</v>
-      </c>
-    </row>
-    <row r="189" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="189" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A189">
         <v>-3056.3335942277699</v>
       </c>
@@ -6462,12 +5474,8 @@
       <c r="F189">
         <v>4491.0406669690901</v>
       </c>
-      <c r="H189">
-        <f t="shared" si="2"/>
-        <v>702.88008591163452</v>
-      </c>
-    </row>
-    <row r="190" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="190" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A190">
         <v>-3048.3688823380498</v>
       </c>
@@ -6486,12 +5494,8 @@
       <c r="F190">
         <v>5000</v>
       </c>
-      <c r="H190">
-        <f t="shared" si="2"/>
-        <v>4466.3387119690506</v>
-      </c>
-    </row>
-    <row r="191" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="191" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A191">
         <v>-2994.47150044517</v>
       </c>
@@ -6510,12 +5514,8 @@
       <c r="F191">
         <v>953.93370430192704</v>
       </c>
-      <c r="H191">
-        <f t="shared" si="2"/>
-        <v>984.33972830584571</v>
-      </c>
-    </row>
-    <row r="192" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="192" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A192">
         <v>-2986.5101104104801</v>
       </c>
@@ -6534,12 +5534,8 @@
       <c r="F192">
         <v>3141.19026100985</v>
       </c>
-      <c r="H192">
-        <f t="shared" si="2"/>
-        <v>5000.0000000000009</v>
-      </c>
-    </row>
-    <row r="193" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="193" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A193">
         <v>-2986.31280160509</v>
       </c>
@@ -6558,12 +5554,8 @@
       <c r="F193">
         <v>-1058.06419478782</v>
       </c>
-      <c r="H193">
-        <f t="shared" si="2"/>
-        <v>4999.9999999999982</v>
-      </c>
-    </row>
-    <row r="194" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="194" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A194">
         <v>-2969.4025012649599</v>
       </c>
@@ -6582,12 +5574,8 @@
       <c r="F194">
         <v>5000</v>
       </c>
-      <c r="H194">
-        <f t="shared" si="2"/>
-        <v>4728.5875931399678</v>
-      </c>
-    </row>
-    <row r="195" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="195" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A195">
         <v>-2968.7370855588601</v>
       </c>
@@ -6606,12 +5594,8 @@
       <c r="F195">
         <v>-2343.4120765821799</v>
       </c>
-      <c r="H195">
-        <f t="shared" si="2"/>
-        <v>4999.9999999999973</v>
-      </c>
-    </row>
-    <row r="196" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="196" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A196">
         <v>-2895.9343693692299</v>
       </c>
@@ -6630,12 +5614,8 @@
       <c r="F196">
         <v>-1922.89114920624</v>
       </c>
-      <c r="H196">
-        <f t="shared" si="2"/>
-        <v>4999.9999999999973</v>
-      </c>
-    </row>
-    <row r="197" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="197" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A197">
         <v>-2843.9095604988502</v>
       </c>
@@ -6654,12 +5634,8 @@
       <c r="F197">
         <v>1682.0602833431301</v>
       </c>
-      <c r="H197">
-        <f t="shared" ref="H197:H260" si="3">SQRT((D197-A197)^2+(E197-B197)^2+(F197-C197)^2)</f>
-        <v>3492.9119430693454</v>
-      </c>
-    </row>
-    <row r="198" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="198" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A198">
         <v>-2842.1104848733298</v>
       </c>
@@ -6678,12 +5654,8 @@
       <c r="F198">
         <v>1262.81558483149</v>
       </c>
-      <c r="H198">
-        <f t="shared" si="3"/>
-        <v>4540.8049616439957</v>
-      </c>
-    </row>
-    <row r="199" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="199" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A199">
         <v>-2834.8581106510701</v>
       </c>
@@ -6702,12 +5674,8 @@
       <c r="F199">
         <v>4736.14938638688</v>
       </c>
-      <c r="H199">
-        <f t="shared" si="3"/>
-        <v>2794.3226931075365</v>
-      </c>
-    </row>
-    <row r="200" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="200" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A200">
         <v>-2793.9246851892599</v>
       </c>
@@ -6726,12 +5694,8 @@
       <c r="F200">
         <v>-986.77375054525999</v>
       </c>
-      <c r="H200">
-        <f t="shared" si="3"/>
-        <v>3707.3706554601663</v>
-      </c>
-    </row>
-    <row r="201" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="201" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A201">
         <v>-2792.29860490794</v>
       </c>
@@ -6750,12 +5714,8 @@
       <c r="F201">
         <v>5000</v>
       </c>
-      <c r="H201">
-        <f t="shared" si="3"/>
-        <v>715.98996653289748</v>
-      </c>
-    </row>
-    <row r="202" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="202" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A202">
         <v>-2781.39357265528</v>
       </c>
@@ -6774,12 +5734,8 @@
       <c r="F202">
         <v>-4451.0329233398397</v>
       </c>
-      <c r="H202">
-        <f t="shared" si="3"/>
-        <v>1489.6873403595607</v>
-      </c>
-    </row>
-    <row r="203" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="203" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A203">
         <v>-2746.0169099126801</v>
       </c>
@@ -6798,12 +5754,8 @@
       <c r="F203">
         <v>4032.0536847076</v>
       </c>
-      <c r="H203">
-        <f t="shared" si="3"/>
-        <v>1662.7992908866556</v>
-      </c>
-    </row>
-    <row r="204" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="204" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A204">
         <v>-2735.7386486704099</v>
       </c>
@@ -6822,12 +5774,8 @@
       <c r="F204">
         <v>-4104.9372673023699</v>
       </c>
-      <c r="H204">
-        <f t="shared" si="3"/>
-        <v>5000.0000000000027</v>
-      </c>
-    </row>
-    <row r="205" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="205" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A205">
         <v>-2732.6265597870101</v>
       </c>
@@ -6846,12 +5794,8 @@
       <c r="F205">
         <v>-3660.0385026987401</v>
       </c>
-      <c r="H205">
-        <f t="shared" si="3"/>
-        <v>5000.0000000000018</v>
-      </c>
-    </row>
-    <row r="206" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="206" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A206">
         <v>-2713.5198373742301</v>
       </c>
@@ -6870,12 +5814,8 @@
       <c r="F206">
         <v>-528.99198640816701</v>
       </c>
-      <c r="H206">
-        <f t="shared" si="3"/>
-        <v>4384.0831564086629</v>
-      </c>
-    </row>
-    <row r="207" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="207" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A207">
         <v>-2705.1163518385501</v>
       </c>
@@ -6894,12 +5834,8 @@
       <c r="F207">
         <v>3983.7396750735002</v>
       </c>
-      <c r="H207">
-        <f t="shared" si="3"/>
-        <v>4999.9999999999991</v>
-      </c>
-    </row>
-    <row r="208" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="208" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A208">
         <v>-2677.92026474569</v>
       </c>
@@ -6918,12 +5854,8 @@
       <c r="F208">
         <v>-483.520658819213</v>
       </c>
-      <c r="H208">
-        <f t="shared" si="3"/>
-        <v>5000.0000000000064</v>
-      </c>
-    </row>
-    <row r="209" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="209" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A209">
         <v>-2639.76796077274</v>
       </c>
@@ -6942,12 +5874,8 @@
       <c r="F209">
         <v>5000</v>
       </c>
-      <c r="H209">
-        <f t="shared" si="3"/>
-        <v>4620.6246013451264</v>
-      </c>
-    </row>
-    <row r="210" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="210" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A210">
         <v>-2629.9075124681299</v>
       </c>
@@ -6966,12 +5894,8 @@
       <c r="F210">
         <v>-4650.91555074587</v>
       </c>
-      <c r="H210">
-        <f t="shared" si="3"/>
-        <v>2917.968028483469</v>
-      </c>
-    </row>
-    <row r="211" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="211" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A211">
         <v>-2620.5587430003802</v>
       </c>
@@ -6990,12 +5914,8 @@
       <c r="F211">
         <v>4329.0226265766496</v>
       </c>
-      <c r="H211">
-        <f t="shared" si="3"/>
-        <v>1136.0019572193421</v>
-      </c>
-    </row>
-    <row r="212" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="212" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A212">
         <v>-2558.6184391106699</v>
       </c>
@@ -7014,12 +5934,8 @@
       <c r="F212">
         <v>5000</v>
       </c>
-      <c r="H212">
-        <f t="shared" si="3"/>
-        <v>2939.8940174093791</v>
-      </c>
-    </row>
-    <row r="213" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="213" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A213">
         <v>-2558.2269540324601</v>
       </c>
@@ -7038,12 +5954,8 @@
       <c r="F213">
         <v>-998.57212723790803</v>
       </c>
-      <c r="H213">
-        <f t="shared" si="3"/>
-        <v>4999.9999999999982</v>
-      </c>
-    </row>
-    <row r="214" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="214" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A214">
         <v>-2556.9956644866402</v>
       </c>
@@ -7062,12 +5974,8 @@
       <c r="F214">
         <v>-1324.39072059552</v>
       </c>
-      <c r="H214">
-        <f t="shared" si="3"/>
-        <v>3696.9096317514181</v>
-      </c>
-    </row>
-    <row r="215" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="215" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A215">
         <v>-2520.5950457970198</v>
       </c>
@@ -7086,12 +5994,8 @@
       <c r="F215">
         <v>2627.2201773663501</v>
       </c>
-      <c r="H215">
-        <f t="shared" si="3"/>
-        <v>2801.99766413508</v>
-      </c>
-    </row>
-    <row r="216" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="216" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A216">
         <v>-2514.9777610281999</v>
       </c>
@@ -7110,12 +6014,8 @@
       <c r="F216">
         <v>-2066.9616789152901</v>
       </c>
-      <c r="H216">
-        <f t="shared" si="3"/>
-        <v>5000.0000000000045</v>
-      </c>
-    </row>
-    <row r="217" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="217" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A217">
         <v>-2470.4598403582299</v>
       </c>
@@ -7134,12 +6034,8 @@
       <c r="F217">
         <v>-5000</v>
       </c>
-      <c r="H217">
-        <f t="shared" si="3"/>
-        <v>622.58912645835301</v>
-      </c>
-    </row>
-    <row r="218" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="218" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A218">
         <v>-2446.2731465310699</v>
       </c>
@@ -7158,12 +6054,8 @@
       <c r="F218">
         <v>-2570.5305970663399</v>
       </c>
-      <c r="H218">
-        <f t="shared" si="3"/>
-        <v>4999.9999999999991</v>
-      </c>
-    </row>
-    <row r="219" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="219" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A219">
         <v>-2438.3340319868198</v>
       </c>
@@ -7182,12 +6074,8 @@
       <c r="F219">
         <v>-1495.9019309283799</v>
       </c>
-      <c r="H219">
-        <f t="shared" si="3"/>
-        <v>4123.5000402593705</v>
-      </c>
-    </row>
-    <row r="220" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="220" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A220">
         <v>-2430.3244249568402</v>
       </c>
@@ -7206,12 +6094,8 @@
       <c r="F220">
         <v>-2621.7097147781701</v>
       </c>
-      <c r="H220">
-        <f t="shared" si="3"/>
-        <v>2707.3508171851854</v>
-      </c>
-    </row>
-    <row r="221" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="221" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A221">
         <v>-2429.2543748896201</v>
       </c>
@@ -7230,12 +6114,8 @@
       <c r="F221">
         <v>5000</v>
       </c>
-      <c r="H221">
-        <f t="shared" si="3"/>
-        <v>4587.0763405976986</v>
-      </c>
-    </row>
-    <row r="222" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="222" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A222">
         <v>-2414.4735366648401</v>
       </c>
@@ -7254,12 +6134,8 @@
       <c r="F222">
         <v>-2025.1637457924801</v>
       </c>
-      <c r="H222">
-        <f t="shared" si="3"/>
-        <v>5000.0000000000027</v>
-      </c>
-    </row>
-    <row r="223" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="223" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A223">
         <v>-2406.55684813261</v>
       </c>
@@ -7278,12 +6154,8 @@
       <c r="F223">
         <v>3087.8506263255499</v>
       </c>
-      <c r="H223">
-        <f t="shared" si="3"/>
-        <v>4999.9999999999991</v>
-      </c>
-    </row>
-    <row r="224" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="224" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A224">
         <v>-2404.0049082693299</v>
       </c>
@@ -7302,12 +6174,8 @@
       <c r="F224">
         <v>-1642.9931939492001</v>
       </c>
-      <c r="H224">
-        <f t="shared" si="3"/>
-        <v>4999.9999999999973</v>
-      </c>
-    </row>
-    <row r="225" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="225" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A225">
         <v>-2395.64019653782</v>
       </c>
@@ -7326,12 +6194,8 @@
       <c r="F225">
         <v>4149.2736432315296</v>
       </c>
-      <c r="H225">
-        <f t="shared" si="3"/>
-        <v>5000.0000000000055</v>
-      </c>
-    </row>
-    <row r="226" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="226" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A226">
         <v>-2392.33093833262</v>
       </c>
@@ -7350,12 +6214,8 @@
       <c r="F226">
         <v>1002.08725958384</v>
       </c>
-      <c r="H226">
-        <f t="shared" si="3"/>
-        <v>3042.8166314100226</v>
-      </c>
-    </row>
-    <row r="227" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="227" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A227">
         <v>-2357.3233241509902</v>
       </c>
@@ -7374,12 +6234,8 @@
       <c r="F227">
         <v>-3475.6739575921902</v>
       </c>
-      <c r="H227">
-        <f t="shared" si="3"/>
-        <v>5000.0000000000064</v>
-      </c>
-    </row>
-    <row r="228" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="228" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A228">
         <v>-2345.2812773475898</v>
       </c>
@@ -7398,12 +6254,8 @@
       <c r="F228">
         <v>4210.2805663140598</v>
       </c>
-      <c r="H228">
-        <f t="shared" si="3"/>
-        <v>2347.122112646914</v>
-      </c>
-    </row>
-    <row r="229" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="229" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A229">
         <v>-2318.33342960861</v>
       </c>
@@ -7422,12 +6274,8 @@
       <c r="F229">
         <v>1834.68700274722</v>
       </c>
-      <c r="H229">
-        <f t="shared" si="3"/>
-        <v>2883.4357651842852</v>
-      </c>
-    </row>
-    <row r="230" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="230" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A230">
         <v>-2274.2362073241702</v>
       </c>
@@ -7446,12 +6294,8 @@
       <c r="F230">
         <v>3644.5605447878602</v>
       </c>
-      <c r="H230">
-        <f t="shared" si="3"/>
-        <v>5000.0000000000027</v>
-      </c>
-    </row>
-    <row r="231" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="231" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A231">
         <v>-2273.23100033529</v>
       </c>
@@ -7470,12 +6314,8 @@
       <c r="F231">
         <v>3343.9961412919401</v>
       </c>
-      <c r="H231">
-        <f t="shared" si="3"/>
-        <v>4999.9999999999936</v>
-      </c>
-    </row>
-    <row r="232" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="232" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A232">
         <v>-2254.24596254165</v>
       </c>
@@ -7494,12 +6334,8 @@
       <c r="F232">
         <v>5000</v>
       </c>
-      <c r="H232">
-        <f t="shared" si="3"/>
-        <v>3830.291456970348</v>
-      </c>
-    </row>
-    <row r="233" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="233" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A233">
         <v>-2253.4458059736999</v>
       </c>
@@ -7518,12 +6354,8 @@
       <c r="F233">
         <v>-5000</v>
       </c>
-      <c r="H233">
-        <f t="shared" si="3"/>
-        <v>1778.7016910824266</v>
-      </c>
-    </row>
-    <row r="234" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="234" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A234">
         <v>-2189.8070520021402</v>
       </c>
@@ -7542,12 +6374,8 @@
       <c r="F234">
         <v>-5000</v>
       </c>
-      <c r="H234">
-        <f t="shared" si="3"/>
-        <v>531.64241204376447</v>
-      </c>
-    </row>
-    <row r="235" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="235" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A235">
         <v>-2188.5052422075701</v>
       </c>
@@ -7566,12 +6394,8 @@
       <c r="F235">
         <v>-1336.76737366629</v>
       </c>
-      <c r="H235">
-        <f t="shared" si="3"/>
-        <v>5000.0000000000055</v>
-      </c>
-    </row>
-    <row r="236" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="236" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A236">
         <v>-2170.23239774886</v>
       </c>
@@ -7590,12 +6414,8 @@
       <c r="F236">
         <v>3090.7961614067199</v>
       </c>
-      <c r="H236">
-        <f t="shared" si="3"/>
-        <v>2410.9795098860995</v>
-      </c>
-    </row>
-    <row r="237" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="237" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A237">
         <v>-2166.8812100953701</v>
       </c>
@@ -7614,12 +6434,8 @@
       <c r="F237">
         <v>1792.40410628723</v>
       </c>
-      <c r="H237">
-        <f t="shared" si="3"/>
-        <v>3221.2983089175682</v>
-      </c>
-    </row>
-    <row r="238" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="238" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A238">
         <v>-2152.9173421658302</v>
       </c>
@@ -7638,12 +6454,8 @@
       <c r="F238">
         <v>5000</v>
       </c>
-      <c r="H238">
-        <f t="shared" si="3"/>
-        <v>2257.2584096106448</v>
-      </c>
-    </row>
-    <row r="239" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="239" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A239">
         <v>-2109.6224618833398</v>
       </c>
@@ -7662,12 +6474,8 @@
       <c r="F239">
         <v>3981.9907643986999</v>
       </c>
-      <c r="H239">
-        <f t="shared" si="3"/>
-        <v>1550.389559472771</v>
-      </c>
-    </row>
-    <row r="240" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="240" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A240">
         <v>-2108.2333660864601</v>
       </c>
@@ -7686,12 +6494,8 @@
       <c r="F240">
         <v>350.488670528782</v>
       </c>
-      <c r="H240">
-        <f t="shared" si="3"/>
-        <v>4999.9999999999982</v>
-      </c>
-    </row>
-    <row r="241" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="241" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A241">
         <v>-2074.8217000828799</v>
       </c>
@@ -7710,12 +6514,8 @@
       <c r="F241">
         <v>-3463.5827329071499</v>
       </c>
-      <c r="H241">
-        <f t="shared" si="3"/>
-        <v>3285.7169157896756</v>
-      </c>
-    </row>
-    <row r="242" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="242" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A242">
         <v>-2071.1049254666</v>
       </c>
@@ -7734,12 +6534,8 @@
       <c r="F242">
         <v>-3547.4799129247199</v>
       </c>
-      <c r="H242">
-        <f t="shared" si="3"/>
-        <v>5000.0000000000073</v>
-      </c>
-    </row>
-    <row r="243" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="243" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A243">
         <v>-2033.2836299277101</v>
       </c>
@@ -7758,12 +6554,8 @@
       <c r="F243">
         <v>-912.52370769806305</v>
       </c>
-      <c r="H243">
-        <f t="shared" si="3"/>
-        <v>876.49995974062915</v>
-      </c>
-    </row>
-    <row r="244" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="244" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A244">
         <v>-2033.25644272164</v>
       </c>
@@ -7782,12 +6574,8 @@
       <c r="F244">
         <v>-2650.4908777642599</v>
       </c>
-      <c r="H244">
-        <f t="shared" si="3"/>
-        <v>5000.0000000000045</v>
-      </c>
-    </row>
-    <row r="245" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="245" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A245">
         <v>-2020.0373549655801</v>
       </c>
@@ -7806,12 +6594,8 @@
       <c r="F245">
         <v>-4354.3262658416397</v>
       </c>
-      <c r="H245">
-        <f t="shared" si="3"/>
-        <v>676.80554791869019</v>
-      </c>
-    </row>
-    <row r="246" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="246" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A246">
         <v>-1994.91457542075</v>
       </c>
@@ -7830,12 +6614,8 @@
       <c r="F246">
         <v>5000</v>
       </c>
-      <c r="H246">
-        <f t="shared" si="3"/>
-        <v>1072.0621502569836</v>
-      </c>
-    </row>
-    <row r="247" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="247" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A247">
         <v>-1993.0511691761999</v>
       </c>
@@ -7854,12 +6634,8 @@
       <c r="F247">
         <v>-4871.5640252145704</v>
       </c>
-      <c r="H247">
-        <f t="shared" si="3"/>
-        <v>5000</v>
-      </c>
-    </row>
-    <row r="248" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="248" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A248">
         <v>-1987.8512239419899</v>
       </c>
@@ -7878,12 +6654,8 @@
       <c r="F248">
         <v>-836.83120133333205</v>
       </c>
-      <c r="H248">
-        <f t="shared" si="3"/>
-        <v>2698.8349766717542</v>
-      </c>
-    </row>
-    <row r="249" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="249" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A249">
         <v>-1979.2166521355</v>
       </c>
@@ -7902,12 +6674,8 @@
       <c r="F249">
         <v>-469.25441428632598</v>
       </c>
-      <c r="H249">
-        <f t="shared" si="3"/>
-        <v>4999.9999999999991</v>
-      </c>
-    </row>
-    <row r="250" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="250" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A250">
         <v>-1976.3601228957</v>
       </c>
@@ -7926,12 +6694,8 @@
       <c r="F250">
         <v>-1155.8278398459199</v>
       </c>
-      <c r="H250">
-        <f t="shared" si="3"/>
-        <v>5000.0000000000045</v>
-      </c>
-    </row>
-    <row r="251" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="251" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A251">
         <v>-1967.2058413861701</v>
       </c>
@@ -7950,12 +6714,8 @@
       <c r="F251">
         <v>-35.518782478266502</v>
       </c>
-      <c r="H251">
-        <f t="shared" si="3"/>
-        <v>4941.1498621603614</v>
-      </c>
-    </row>
-    <row r="252" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="252" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A252">
         <v>-1959.7032688218001</v>
       </c>
@@ -7974,12 +6734,8 @@
       <c r="F252">
         <v>4872.1326098092604</v>
       </c>
-      <c r="H252">
-        <f t="shared" si="3"/>
-        <v>5000.0000000000082</v>
-      </c>
-    </row>
-    <row r="253" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="253" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A253">
         <v>-1921.1721436779901</v>
       </c>
@@ -7998,12 +6754,8 @@
       <c r="F253">
         <v>-5000</v>
       </c>
-      <c r="H253">
-        <f t="shared" si="3"/>
-        <v>3981.9000012432466</v>
-      </c>
-    </row>
-    <row r="254" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="254" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A254">
         <v>-1913.9010208391901</v>
       </c>
@@ -8022,12 +6774,8 @@
       <c r="F254">
         <v>-10.895276376742901</v>
       </c>
-      <c r="H254">
-        <f t="shared" si="3"/>
-        <v>615.91684359133956</v>
-      </c>
-    </row>
-    <row r="255" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="255" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A255">
         <v>-1913.6515722947399</v>
       </c>
@@ -8046,12 +6794,8 @@
       <c r="F255">
         <v>-732.67518990504004</v>
       </c>
-      <c r="H255">
-        <f t="shared" si="3"/>
-        <v>5000.0000000000036</v>
-      </c>
-    </row>
-    <row r="256" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="256" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A256">
         <v>-1903.57591142826</v>
       </c>
@@ -8070,12 +6814,8 @@
       <c r="F256">
         <v>-3331.87517089938</v>
       </c>
-      <c r="H256">
-        <f t="shared" si="3"/>
-        <v>787.4885533585616</v>
-      </c>
-    </row>
-    <row r="257" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="257" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A257">
         <v>-1838.8928393874201</v>
       </c>
@@ -8094,12 +6834,8 @@
       <c r="F257">
         <v>-505.90266202047798</v>
       </c>
-      <c r="H257">
-        <f t="shared" si="3"/>
-        <v>5000.0000000000045</v>
-      </c>
-    </row>
-    <row r="258" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="258" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A258">
         <v>-1834.8824757604</v>
       </c>
@@ -8118,12 +6854,8 @@
       <c r="F258">
         <v>-3835.5144257615102</v>
       </c>
-      <c r="H258">
-        <f t="shared" si="3"/>
-        <v>1580.8157370961028</v>
-      </c>
-    </row>
-    <row r="259" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="259" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A259">
         <v>-1827.4342002489</v>
       </c>
@@ -8142,12 +6874,8 @@
       <c r="F259">
         <v>1733.6325325922301</v>
       </c>
-      <c r="H259">
-        <f t="shared" si="3"/>
-        <v>5000.0000000000009</v>
-      </c>
-    </row>
-    <row r="260" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="260" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A260">
         <v>-1825.07983650809</v>
       </c>
@@ -8166,12 +6894,8 @@
       <c r="F260">
         <v>4483.3560037112102</v>
       </c>
-      <c r="H260">
-        <f t="shared" si="3"/>
-        <v>2089.1911043119117</v>
-      </c>
-    </row>
-    <row r="261" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="261" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A261">
         <v>-1824.9495825332001</v>
       </c>
@@ -8190,12 +6914,8 @@
       <c r="F261">
         <v>111.82155869408599</v>
       </c>
-      <c r="H261">
-        <f t="shared" ref="H261:H324" si="4">SQRT((D261-A261)^2+(E261-B261)^2+(F261-C261)^2)</f>
-        <v>4999.9999999999991</v>
-      </c>
-    </row>
-    <row r="262" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="262" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A262">
         <v>-1804.4349664292899</v>
       </c>
@@ -8214,12 +6934,8 @@
       <c r="F262">
         <v>-3998.83357329502</v>
       </c>
-      <c r="H262">
-        <f t="shared" si="4"/>
-        <v>5000</v>
-      </c>
-    </row>
-    <row r="263" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="263" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A263">
         <v>-1768.3663108666799</v>
       </c>
@@ -8238,12 +6954,8 @@
       <c r="F263">
         <v>-936.91432976050703</v>
       </c>
-      <c r="H263">
-        <f t="shared" si="4"/>
-        <v>4999.9999999999991</v>
-      </c>
-    </row>
-    <row r="264" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="264" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A264">
         <v>-1760.28009020591</v>
       </c>
@@ -8262,12 +6974,8 @@
       <c r="F264">
         <v>-2015.1277246330001</v>
       </c>
-      <c r="H264">
-        <f t="shared" si="4"/>
-        <v>5000.0000000000045</v>
-      </c>
-    </row>
-    <row r="265" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="265" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A265">
         <v>-1723.7941228873201</v>
       </c>
@@ -8286,12 +6994,8 @@
       <c r="F265">
         <v>-3921.6902929328298</v>
       </c>
-      <c r="H265">
-        <f t="shared" si="4"/>
-        <v>2060.1059825906227</v>
-      </c>
-    </row>
-    <row r="266" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="266" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A266">
         <v>-1714.324078827</v>
       </c>
@@ -8310,12 +7014,8 @@
       <c r="F266">
         <v>-4406.6304640198196</v>
       </c>
-      <c r="H266">
-        <f t="shared" si="4"/>
-        <v>5000.0000000000036</v>
-      </c>
-    </row>
-    <row r="267" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="267" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A267">
         <v>-1696.8572692888199</v>
       </c>
@@ -8334,12 +7034,8 @@
       <c r="F267">
         <v>4405.3871272052602</v>
       </c>
-      <c r="H267">
-        <f t="shared" si="4"/>
-        <v>4999.9999999999964</v>
-      </c>
-    </row>
-    <row r="268" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="268" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A268">
         <v>-1688.0267510973299</v>
       </c>
@@ -8358,12 +7054,8 @@
       <c r="F268">
         <v>-1901.40221934895</v>
       </c>
-      <c r="H268">
-        <f t="shared" si="4"/>
-        <v>4999.9999999999927</v>
-      </c>
-    </row>
-    <row r="269" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="269" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A269">
         <v>-1687.9610282177</v>
       </c>
@@ -8382,12 +7074,8 @@
       <c r="F269">
         <v>1093.21147565664</v>
       </c>
-      <c r="H269">
-        <f t="shared" si="4"/>
-        <v>4957.3392906708923</v>
-      </c>
-    </row>
-    <row r="270" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="270" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A270">
         <v>-1678.8429893407599</v>
       </c>
@@ -8406,12 +7094,8 @@
       <c r="F270">
         <v>243.579738289891</v>
       </c>
-      <c r="H270">
-        <f t="shared" si="4"/>
-        <v>4844.1684464324107</v>
-      </c>
-    </row>
-    <row r="271" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="271" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A271">
         <v>-1668.94292631907</v>
       </c>
@@ -8430,12 +7114,8 @@
       <c r="F271">
         <v>5000</v>
       </c>
-      <c r="H271">
-        <f t="shared" si="4"/>
-        <v>4267.8111964917844</v>
-      </c>
-    </row>
-    <row r="272" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="272" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A272">
         <v>-1638.2138106544501</v>
       </c>
@@ -8454,12 +7134,8 @@
       <c r="F272">
         <v>707.56464235511305</v>
       </c>
-      <c r="H272">
-        <f t="shared" si="4"/>
-        <v>5000.0000000000018</v>
-      </c>
-    </row>
-    <row r="273" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="273" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A273">
         <v>-1630.7943849419501</v>
       </c>
@@ -8478,12 +7154,8 @@
       <c r="F273">
         <v>-4331.0400569522999</v>
       </c>
-      <c r="H273">
-        <f t="shared" si="4"/>
-        <v>3930.0211394368885</v>
-      </c>
-    </row>
-    <row r="274" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="274" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A274">
         <v>-1606.5017931253101</v>
       </c>
@@ -8502,12 +7174,8 @@
       <c r="F274">
         <v>-782.800940765375</v>
       </c>
-      <c r="H274">
-        <f t="shared" si="4"/>
-        <v>2806.5651097772698</v>
-      </c>
-    </row>
-    <row r="275" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="275" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A275">
         <v>-1592.7428138185001</v>
       </c>
@@ -8526,12 +7194,8 @@
       <c r="F275">
         <v>-51.118607928260197</v>
       </c>
-      <c r="H275">
-        <f t="shared" si="4"/>
-        <v>4212.5114466414361</v>
-      </c>
-    </row>
-    <row r="276" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="276" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A276">
         <v>-1574.6598139130699</v>
       </c>
@@ -8550,12 +7214,8 @@
       <c r="F276">
         <v>-1805.5590429384199</v>
       </c>
-      <c r="H276">
-        <f t="shared" si="4"/>
-        <v>5000.0000000000045</v>
-      </c>
-    </row>
-    <row r="277" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="277" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A277">
         <v>-1561.9368141303</v>
       </c>
@@ -8574,12 +7234,8 @@
       <c r="F277">
         <v>3618.8210005627998</v>
       </c>
-      <c r="H277">
-        <f t="shared" si="4"/>
-        <v>5000.0000000000064</v>
-      </c>
-    </row>
-    <row r="278" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="278" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A278">
         <v>-1548.58886727104</v>
       </c>
@@ -8598,12 +7254,8 @@
       <c r="F278">
         <v>-4793.0384740966101</v>
       </c>
-      <c r="H278">
-        <f t="shared" si="4"/>
-        <v>5000.0000000000036</v>
-      </c>
-    </row>
-    <row r="279" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="279" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A279">
         <v>-1538.64137353927</v>
       </c>
@@ -8622,12 +7274,8 @@
       <c r="F279">
         <v>5000</v>
       </c>
-      <c r="H279">
-        <f t="shared" si="4"/>
-        <v>2874.3498682938366</v>
-      </c>
-    </row>
-    <row r="280" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="280" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A280">
         <v>-1489.5706179527899</v>
       </c>
@@ -8646,12 +7294,8 @@
       <c r="F280">
         <v>943.60952553364905</v>
       </c>
-      <c r="H280">
-        <f t="shared" si="4"/>
-        <v>4999.9999999999973</v>
-      </c>
-    </row>
-    <row r="281" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="281" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A281">
         <v>-1465.6723208824701</v>
       </c>
@@ -8670,12 +7314,8 @@
       <c r="F281">
         <v>-209.54797739173301</v>
       </c>
-      <c r="H281">
-        <f t="shared" si="4"/>
-        <v>4118.7372743169044</v>
-      </c>
-    </row>
-    <row r="282" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="282" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A282">
         <v>-1462.5326550549</v>
       </c>
@@ -8694,12 +7334,8 @@
       <c r="F282">
         <v>4998.7729355247202</v>
       </c>
-      <c r="H282">
-        <f t="shared" si="4"/>
-        <v>4999.9999999999982</v>
-      </c>
-    </row>
-    <row r="283" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="283" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A283">
         <v>-1410.4247519826999</v>
       </c>
@@ -8718,12 +7354,8 @@
       <c r="F283">
         <v>2312.1528770731502</v>
       </c>
-      <c r="H283">
-        <f t="shared" si="4"/>
-        <v>3260.3548601224456</v>
-      </c>
-    </row>
-    <row r="284" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="284" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A284">
         <v>-1370.4767329552201</v>
       </c>
@@ -8742,12 +7374,8 @@
       <c r="F284">
         <v>-692.04078567967304</v>
       </c>
-      <c r="H284">
-        <f t="shared" si="4"/>
-        <v>5000</v>
-      </c>
-    </row>
-    <row r="285" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="285" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A285">
         <v>-1347.78169267974</v>
       </c>
@@ -8766,12 +7394,8 @@
       <c r="F285">
         <v>-4536.9045187376896</v>
       </c>
-      <c r="H285">
-        <f t="shared" si="4"/>
-        <v>1079.9422995026966</v>
-      </c>
-    </row>
-    <row r="286" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="286" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A286">
         <v>-1289.8534848122499</v>
       </c>
@@ -8790,12 +7414,8 @@
       <c r="F286">
         <v>-141.12538836423499</v>
       </c>
-      <c r="H286">
-        <f t="shared" si="4"/>
-        <v>4999.9999999999945</v>
-      </c>
-    </row>
-    <row r="287" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="287" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A287">
         <v>-1287.5492143397</v>
       </c>
@@ -8814,12 +7434,8 @@
       <c r="F287">
         <v>-786.77395437138705</v>
       </c>
-      <c r="H287">
-        <f t="shared" si="4"/>
-        <v>4999.9999999999982</v>
-      </c>
-    </row>
-    <row r="288" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="288" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A288">
         <v>-1195.8650828647501</v>
       </c>
@@ -8838,12 +7454,8 @@
       <c r="F288">
         <v>-2931.5724865881698</v>
       </c>
-      <c r="H288">
-        <f t="shared" si="4"/>
-        <v>5000.0000000000018</v>
-      </c>
-    </row>
-    <row r="289" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="289" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A289">
         <v>-1191.0644742537399</v>
       </c>
@@ -8862,12 +7474,8 @@
       <c r="F289">
         <v>3141.4857306137101</v>
       </c>
-      <c r="H289">
-        <f t="shared" si="4"/>
-        <v>5000.0000000000027</v>
-      </c>
-    </row>
-    <row r="290" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="290" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A290">
         <v>-1172.3782129547701</v>
       </c>
@@ -8886,12 +7494,8 @@
       <c r="F290">
         <v>-250.51899563684501</v>
       </c>
-      <c r="H290">
-        <f t="shared" si="4"/>
-        <v>5000.0000000000018</v>
-      </c>
-    </row>
-    <row r="291" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="291" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A291">
         <v>-1164.2172237243799</v>
       </c>
@@ -8910,12 +7514,8 @@
       <c r="F291">
         <v>-1200.2574878045</v>
       </c>
-      <c r="H291">
-        <f t="shared" si="4"/>
-        <v>4999.9999999999909</v>
-      </c>
-    </row>
-    <row r="292" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="292" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A292">
         <v>-1139.2856415513299</v>
       </c>
@@ -8934,12 +7534,8 @@
       <c r="F292">
         <v>-4343.2947985575202</v>
       </c>
-      <c r="H292">
-        <f t="shared" si="4"/>
-        <v>1063.9379703076745</v>
-      </c>
-    </row>
-    <row r="293" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="293" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A293">
         <v>-1122.3199657006101</v>
       </c>
@@ -8958,12 +7554,8 @@
       <c r="F293">
         <v>-3791.6125518898398</v>
       </c>
-      <c r="H293">
-        <f t="shared" si="4"/>
-        <v>5000.0000000000018</v>
-      </c>
-    </row>
-    <row r="294" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="294" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A294">
         <v>-1115.6291868078599</v>
       </c>
@@ -8982,12 +7574,8 @@
       <c r="F294">
         <v>-5000</v>
       </c>
-      <c r="H294">
-        <f t="shared" si="4"/>
-        <v>664.57180428763422</v>
-      </c>
-    </row>
-    <row r="295" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="295" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A295">
         <v>-1061.3539568450601</v>
       </c>
@@ -9006,12 +7594,8 @@
       <c r="F295">
         <v>-4097.63570738216</v>
       </c>
-      <c r="H295">
-        <f t="shared" si="4"/>
-        <v>5000</v>
-      </c>
-    </row>
-    <row r="296" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="296" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A296">
         <v>-1042.3538704186501</v>
       </c>
@@ -9030,12 +7614,8 @@
       <c r="F296">
         <v>-3435.4682595444701</v>
       </c>
-      <c r="H296">
-        <f t="shared" si="4"/>
-        <v>5000</v>
-      </c>
-    </row>
-    <row r="297" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="297" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A297">
         <v>-1029.0689812948001</v>
       </c>
@@ -9054,12 +7634,8 @@
       <c r="F297">
         <v>-4391.0902097524904</v>
       </c>
-      <c r="H297">
-        <f t="shared" si="4"/>
-        <v>4847.9295651263537</v>
-      </c>
-    </row>
-    <row r="298" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="298" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A298">
         <v>-1021.46911361414</v>
       </c>
@@ -9078,12 +7654,8 @@
       <c r="F298">
         <v>-3465.5474303225501</v>
       </c>
-      <c r="H298">
-        <f t="shared" si="4"/>
-        <v>5000.0000000000036</v>
-      </c>
-    </row>
-    <row r="299" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="299" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A299">
         <v>-1007.6001228256901</v>
       </c>
@@ -9102,12 +7674,8 @@
       <c r="F299">
         <v>1533.6206265558401</v>
       </c>
-      <c r="H299">
-        <f t="shared" si="4"/>
-        <v>1966.4313636555473</v>
-      </c>
-    </row>
-    <row r="300" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="300" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A300">
         <v>-1001.0229248571</v>
       </c>
@@ -9126,12 +7694,8 @@
       <c r="F300">
         <v>-356.80817402924998</v>
       </c>
-      <c r="H300">
-        <f t="shared" si="4"/>
-        <v>5000.0000000000027</v>
-      </c>
-    </row>
-    <row r="301" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="301" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A301">
         <v>-950.25729614407805</v>
       </c>
@@ -9150,12 +7714,8 @@
       <c r="F301">
         <v>-119.14889000828499</v>
       </c>
-      <c r="H301">
-        <f t="shared" si="4"/>
-        <v>5000.0000000000018</v>
-      </c>
-    </row>
-    <row r="302" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="302" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A302">
         <v>-949.22480432159</v>
       </c>
@@ -9174,12 +7734,8 @@
       <c r="F302">
         <v>-4848.2216282210202</v>
       </c>
-      <c r="H302">
-        <f t="shared" si="4"/>
-        <v>1069.9788605631147</v>
-      </c>
-    </row>
-    <row r="303" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="303" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A303">
         <v>-943.88304787991297</v>
       </c>
@@ -9198,12 +7754,8 @@
       <c r="F303">
         <v>-3395.2895584380399</v>
       </c>
-      <c r="H303">
-        <f t="shared" si="4"/>
-        <v>3658.6314329985971</v>
-      </c>
-    </row>
-    <row r="304" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="304" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A304">
         <v>-939.62119761665394</v>
       </c>
@@ -9222,12 +7774,8 @@
       <c r="F304">
         <v>-1223.8448689366601</v>
       </c>
-      <c r="H304">
-        <f t="shared" si="4"/>
-        <v>1454.100964905545</v>
-      </c>
-    </row>
-    <row r="305" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="305" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A305">
         <v>-924.11699247487195</v>
       </c>
@@ -9246,12 +7794,8 @@
       <c r="F305">
         <v>408.86061161699502</v>
       </c>
-      <c r="H305">
-        <f t="shared" si="4"/>
-        <v>5000.0000000000009</v>
-      </c>
-    </row>
-    <row r="306" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="306" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A306">
         <v>-921.72308116687395</v>
       </c>
@@ -9270,12 +7814,8 @@
       <c r="F306">
         <v>2502.4048666386002</v>
       </c>
-      <c r="H306">
-        <f t="shared" si="4"/>
-        <v>2198.0023358649228</v>
-      </c>
-    </row>
-    <row r="307" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="307" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A307">
         <v>-910.64349686362903</v>
       </c>
@@ -9294,12 +7834,8 @@
       <c r="F307">
         <v>-940.52670221845403</v>
       </c>
-      <c r="H307">
-        <f t="shared" si="4"/>
-        <v>4999.9999999999964</v>
-      </c>
-    </row>
-    <row r="308" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="308" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A308">
         <v>-908.52473449358899</v>
       </c>
@@ -9318,12 +7854,8 @@
       <c r="F308">
         <v>2862.4966206387999</v>
       </c>
-      <c r="H308">
-        <f t="shared" si="4"/>
-        <v>5000.0000000000027</v>
-      </c>
-    </row>
-    <row r="309" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="309" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A309">
         <v>-885.05274629301005</v>
       </c>
@@ -9342,12 +7874,8 @@
       <c r="F309">
         <v>-2731.3503178884698</v>
       </c>
-      <c r="H309">
-        <f t="shared" si="4"/>
-        <v>3545.8990350944555</v>
-      </c>
-    </row>
-    <row r="310" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="310" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A310">
         <v>-859.66131957778998</v>
       </c>
@@ -9366,12 +7894,8 @@
       <c r="F310">
         <v>2953.6686738592798</v>
       </c>
-      <c r="H310">
-        <f t="shared" si="4"/>
-        <v>4335.4281957123703</v>
-      </c>
-    </row>
-    <row r="311" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="311" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A311">
         <v>-816.78655234095504</v>
       </c>
@@ -9390,12 +7914,8 @@
       <c r="F311">
         <v>4875.7328130046199</v>
       </c>
-      <c r="H311">
-        <f t="shared" si="4"/>
-        <v>4999.9999999999973</v>
-      </c>
-    </row>
-    <row r="312" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="312" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A312">
         <v>-777.43432967614899</v>
       </c>
@@ -9414,12 +7934,8 @@
       <c r="F312">
         <v>2303.8648474909501</v>
       </c>
-      <c r="H312">
-        <f t="shared" si="4"/>
-        <v>1739.6451398775621</v>
-      </c>
-    </row>
-    <row r="313" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="313" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A313">
         <v>-775.31250668446501</v>
       </c>
@@ -9438,12 +7954,8 @@
       <c r="F313">
         <v>5000</v>
       </c>
-      <c r="H313">
-        <f t="shared" si="4"/>
-        <v>3273.0231007313041</v>
-      </c>
-    </row>
-    <row r="314" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="314" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A314">
         <v>-720.66295949891105</v>
       </c>
@@ -9462,12 +7974,8 @@
       <c r="F314">
         <v>-3852.7192993988401</v>
       </c>
-      <c r="H314">
-        <f t="shared" si="4"/>
-        <v>4999.9999999999991</v>
-      </c>
-    </row>
-    <row r="315" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="315" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A315">
         <v>-704.26011590516998</v>
       </c>
@@ -9486,12 +7994,8 @@
       <c r="F315">
         <v>-2501.8689181763398</v>
       </c>
-      <c r="H315">
-        <f t="shared" si="4"/>
-        <v>5000</v>
-      </c>
-    </row>
-    <row r="316" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="316" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A316">
         <v>-658.66688430965098</v>
       </c>
@@ -9510,12 +8014,8 @@
       <c r="F316">
         <v>-1839.3001927787</v>
       </c>
-      <c r="H316">
-        <f t="shared" si="4"/>
-        <v>4793.5041798796829</v>
-      </c>
-    </row>
-    <row r="317" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="317" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A317">
         <v>-650.51182860423103</v>
       </c>
@@ -9534,12 +8034,8 @@
       <c r="F317">
         <v>1745.22472285259</v>
       </c>
-      <c r="H317">
-        <f t="shared" si="4"/>
-        <v>1957.183368589971</v>
-      </c>
-    </row>
-    <row r="318" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="318" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A318">
         <v>-628.30313143745798</v>
       </c>
@@ -9558,12 +8054,8 @@
       <c r="F318">
         <v>-111.406247731752</v>
       </c>
-      <c r="H318">
-        <f t="shared" si="4"/>
-        <v>5000</v>
-      </c>
-    </row>
-    <row r="319" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="319" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A319">
         <v>-611.89762766097704</v>
       </c>
@@ -9582,12 +8074,8 @@
       <c r="F319">
         <v>5000</v>
       </c>
-      <c r="H319">
-        <f t="shared" si="4"/>
-        <v>2629.6179447387485</v>
-      </c>
-    </row>
-    <row r="320" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="320" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A320">
         <v>-600.29352409933699</v>
       </c>
@@ -9606,12 +8094,8 @@
       <c r="F320">
         <v>-498.47068404967501</v>
       </c>
-      <c r="H320">
-        <f t="shared" si="4"/>
-        <v>5000.0000000000036</v>
-      </c>
-    </row>
-    <row r="321" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="321" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A321">
         <v>-541.38969654484799</v>
       </c>
@@ -9630,12 +8114,8 @@
       <c r="F321">
         <v>-376.30118647081099</v>
       </c>
-      <c r="H321">
-        <f t="shared" si="4"/>
-        <v>4999.9999999999991</v>
-      </c>
-    </row>
-    <row r="322" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="322" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A322">
         <v>-533.71000797197905</v>
       </c>
@@ -9654,12 +8134,8 @@
       <c r="F322">
         <v>1967.3258738493</v>
       </c>
-      <c r="H322">
-        <f t="shared" si="4"/>
-        <v>5000.0000000000018</v>
-      </c>
-    </row>
-    <row r="323" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="323" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A323">
         <v>-514.14167947180897</v>
       </c>
@@ -9678,12 +8154,8 @@
       <c r="F323">
         <v>-5000</v>
       </c>
-      <c r="H323">
-        <f t="shared" si="4"/>
-        <v>3979.1830896616257</v>
-      </c>
-    </row>
-    <row r="324" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="324" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A324">
         <v>-503.31627771601899</v>
       </c>
@@ -9702,12 +8174,8 @@
       <c r="F324">
         <v>-454.57799194418101</v>
       </c>
-      <c r="H324">
-        <f t="shared" si="4"/>
-        <v>4999.9999999999955</v>
-      </c>
-    </row>
-    <row r="325" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="325" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A325">
         <v>-465.37295551857397</v>
       </c>
@@ -9726,12 +8194,8 @@
       <c r="F325">
         <v>-1414.5736986837601</v>
       </c>
-      <c r="H325">
-        <f t="shared" ref="H325:H388" si="5">SQRT((D325-A325)^2+(E325-B325)^2+(F325-C325)^2)</f>
-        <v>5000.0000000000036</v>
-      </c>
-    </row>
-    <row r="326" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="326" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A326">
         <v>-436.45535504926602</v>
       </c>
@@ -9750,12 +8214,8 @@
       <c r="F326">
         <v>-2710.9883781388799</v>
       </c>
-      <c r="H326">
-        <f t="shared" si="5"/>
-        <v>5000.0000000000064</v>
-      </c>
-    </row>
-    <row r="327" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="327" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A327">
         <v>-425.68508376320199</v>
       </c>
@@ -9774,12 +8234,8 @@
       <c r="F327">
         <v>-106.040357091689</v>
       </c>
-      <c r="H327">
-        <f t="shared" si="5"/>
-        <v>4998.981194218999</v>
-      </c>
-    </row>
-    <row r="328" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="328" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A328">
         <v>-418.74576243274998</v>
       </c>
@@ -9798,12 +8254,8 @@
       <c r="F328">
         <v>-3523.1585109621601</v>
       </c>
-      <c r="H328">
-        <f t="shared" si="5"/>
-        <v>5000.0000000000027</v>
-      </c>
-    </row>
-    <row r="329" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="329" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A329">
         <v>-414.14735912800899</v>
       </c>
@@ -9822,12 +8274,8 @@
       <c r="F329">
         <v>-4901.61192915214</v>
       </c>
-      <c r="H329">
-        <f t="shared" si="5"/>
-        <v>4999.9999999999982</v>
-      </c>
-    </row>
-    <row r="330" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="330" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A330">
         <v>-403.88275820486001</v>
       </c>
@@ -9846,12 +8294,8 @@
       <c r="F330">
         <v>699.42003095874702</v>
       </c>
-      <c r="H330">
-        <f t="shared" si="5"/>
-        <v>4999.9999999999982</v>
-      </c>
-    </row>
-    <row r="331" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="331" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A331">
         <v>-397.87595802351098</v>
       </c>
@@ -9870,12 +8314,8 @@
       <c r="F331">
         <v>390.640795228022</v>
       </c>
-      <c r="H331">
-        <f t="shared" si="5"/>
-        <v>5000.0000000000055</v>
-      </c>
-    </row>
-    <row r="332" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="332" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A332">
         <v>-392.074020409426</v>
       </c>
@@ -9894,12 +8334,8 @@
       <c r="F332">
         <v>-2038.3165604006999</v>
       </c>
-      <c r="H332">
-        <f t="shared" si="5"/>
-        <v>4581.838530702641</v>
-      </c>
-    </row>
-    <row r="333" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="333" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A333">
         <v>-381.46727629610899</v>
       </c>
@@ -9918,12 +8354,8 @@
       <c r="F333">
         <v>-1267.8243246482</v>
       </c>
-      <c r="H333">
-        <f t="shared" si="5"/>
-        <v>5000</v>
-      </c>
-    </row>
-    <row r="334" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="334" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A334">
         <v>-371.3647187537</v>
       </c>
@@ -9942,12 +8374,8 @@
       <c r="F334">
         <v>-5000</v>
       </c>
-      <c r="H334">
-        <f t="shared" si="5"/>
-        <v>1391.5287687710995</v>
-      </c>
-    </row>
-    <row r="335" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="335" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A335">
         <v>-368.86590215003599</v>
       </c>
@@ -9966,12 +8394,8 @@
       <c r="F335">
         <v>2467.1448595912102</v>
       </c>
-      <c r="H335">
-        <f t="shared" si="5"/>
-        <v>5000.0000000000045</v>
-      </c>
-    </row>
-    <row r="336" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="336" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A336">
         <v>-330.44785817987099</v>
       </c>
@@ -9990,12 +8414,8 @@
       <c r="F336">
         <v>-5000</v>
       </c>
-      <c r="H336">
-        <f t="shared" si="5"/>
-        <v>3521.7997631268254</v>
-      </c>
-    </row>
-    <row r="337" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="337" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A337">
         <v>-329.18098838902699</v>
       </c>
@@ -10014,12 +8434,8 @@
       <c r="F337">
         <v>3529.8177501643499</v>
       </c>
-      <c r="H337">
-        <f t="shared" si="5"/>
-        <v>3608.4712312288921</v>
-      </c>
-    </row>
-    <row r="338" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="338" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A338">
         <v>-282.13579083582601</v>
       </c>
@@ -10038,12 +8454,8 @@
       <c r="F338">
         <v>595.65972672838802</v>
       </c>
-      <c r="H338">
-        <f t="shared" si="5"/>
-        <v>4999.9999999999955</v>
-      </c>
-    </row>
-    <row r="339" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="339" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A339">
         <v>-270.57823381854899</v>
       </c>
@@ -10062,12 +8474,8 @@
       <c r="F339">
         <v>-2032.0855062674</v>
       </c>
-      <c r="H339">
-        <f t="shared" si="5"/>
-        <v>5000</v>
-      </c>
-    </row>
-    <row r="340" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="340" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A340">
         <v>-203.02237769658299</v>
       </c>
@@ -10086,12 +8494,8 @@
       <c r="F340">
         <v>4133.1905193449402</v>
       </c>
-      <c r="H340">
-        <f t="shared" si="5"/>
-        <v>5000.0000000000045</v>
-      </c>
-    </row>
-    <row r="341" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="341" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A341">
         <v>-185.83447162304799</v>
       </c>
@@ -10110,12 +8514,8 @@
       <c r="F341">
         <v>-442.24756683155903</v>
       </c>
-      <c r="H341">
-        <f t="shared" si="5"/>
-        <v>5000.0000000000036</v>
-      </c>
-    </row>
-    <row r="342" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="342" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A342">
         <v>-155.29396134839601</v>
       </c>
@@ -10134,12 +8534,8 @@
       <c r="F342">
         <v>-1072.44733007642</v>
       </c>
-      <c r="H342">
-        <f t="shared" si="5"/>
-        <v>5000.0000000000045</v>
-      </c>
-    </row>
-    <row r="343" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="343" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A343">
         <v>-86.145555504771394</v>
       </c>
@@ -10158,12 +8554,8 @@
       <c r="F343">
         <v>657.01294202811698</v>
       </c>
-      <c r="H343">
-        <f t="shared" si="5"/>
-        <v>4999.9999999999945</v>
-      </c>
-    </row>
-    <row r="344" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="344" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A344">
         <v>-81.728243759950601</v>
       </c>
@@ -10182,12 +8574,8 @@
       <c r="F344">
         <v>-1619.36362320694</v>
       </c>
-      <c r="H344">
-        <f t="shared" si="5"/>
-        <v>1427.4386735452792</v>
-      </c>
-    </row>
-    <row r="345" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="345" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A345">
         <v>-63.0604605725512</v>
       </c>
@@ -10206,12 +8594,8 @@
       <c r="F345">
         <v>897.41901869370702</v>
       </c>
-      <c r="H345">
-        <f t="shared" si="5"/>
-        <v>5000</v>
-      </c>
-    </row>
-    <row r="346" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="346" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A346">
         <v>-38.440887681171297</v>
       </c>
@@ -10230,12 +8614,8 @@
       <c r="F346">
         <v>-3286.24704548102</v>
       </c>
-      <c r="H346">
-        <f t="shared" si="5"/>
-        <v>4999.9999999999982</v>
-      </c>
-    </row>
-    <row r="347" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="347" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A347">
         <v>-9.3366482178408905</v>
       </c>
@@ -10254,12 +8634,8 @@
       <c r="F347">
         <v>-3249.9776509789699</v>
       </c>
-      <c r="H347">
-        <f t="shared" si="5"/>
-        <v>2370.3820552612433</v>
-      </c>
-    </row>
-    <row r="348" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="348" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A348">
         <v>-2.8367537409094399</v>
       </c>
@@ -10278,12 +8654,8 @@
       <c r="F348">
         <v>-5000</v>
       </c>
-      <c r="H348">
-        <f t="shared" si="5"/>
-        <v>827.21334449867823</v>
-      </c>
-    </row>
-    <row r="349" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="349" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A349">
         <v>92.014523692065296</v>
       </c>
@@ -10302,12 +8674,8 @@
       <c r="F349">
         <v>4760.3464097954702</v>
       </c>
-      <c r="H349">
-        <f t="shared" si="5"/>
-        <v>5000.0000000000018</v>
-      </c>
-    </row>
-    <row r="350" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="350" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A350">
         <v>106.998054848587</v>
       </c>
@@ -10326,12 +8694,8 @@
       <c r="F350">
         <v>1352.8572340565599</v>
       </c>
-      <c r="H350">
-        <f t="shared" si="5"/>
-        <v>5000</v>
-      </c>
-    </row>
-    <row r="351" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="351" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A351">
         <v>127.47594178967999</v>
       </c>
@@ -10350,12 +8714,8 @@
       <c r="F351">
         <v>-4905.4260895206799</v>
       </c>
-      <c r="H351">
-        <f t="shared" si="5"/>
-        <v>667.48850604692086</v>
-      </c>
-    </row>
-    <row r="352" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="352" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A352">
         <v>156.891365494355</v>
       </c>
@@ -10374,12 +8734,8 @@
       <c r="F352">
         <v>3939.4991224938799</v>
       </c>
-      <c r="H352">
-        <f t="shared" si="5"/>
-        <v>1156.5028968025476</v>
-      </c>
-    </row>
-    <row r="353" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="353" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A353">
         <v>211.14824082142101</v>
       </c>
@@ -10398,12 +8754,8 @@
       <c r="F353">
         <v>-2747.1073750585701</v>
       </c>
-      <c r="H353">
-        <f t="shared" si="5"/>
-        <v>4937.9056542645312</v>
-      </c>
-    </row>
-    <row r="354" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="354" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A354">
         <v>231.67270270043699</v>
       </c>
@@ -10422,12 +8774,8 @@
       <c r="F354">
         <v>-1215.9329266345301</v>
       </c>
-      <c r="H354">
-        <f t="shared" si="5"/>
-        <v>1995.4609913414445</v>
-      </c>
-    </row>
-    <row r="355" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="355" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A355">
         <v>254.41793273460999</v>
       </c>
@@ -10446,12 +8794,8 @@
       <c r="F355">
         <v>2208.9598718571901</v>
       </c>
-      <c r="H355">
-        <f t="shared" si="5"/>
-        <v>4999.9999999999973</v>
-      </c>
-    </row>
-    <row r="356" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="356" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A356">
         <v>276.48379297438498</v>
       </c>
@@ -10470,12 +8814,8 @@
       <c r="F356">
         <v>2485.5519088633</v>
       </c>
-      <c r="H356">
-        <f t="shared" si="5"/>
-        <v>4172.7866555013225</v>
-      </c>
-    </row>
-    <row r="357" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="357" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A357">
         <v>356.77403727077501</v>
       </c>
@@ -10494,12 +8834,8 @@
       <c r="F357">
         <v>-3403.1521109325899</v>
       </c>
-      <c r="H357">
-        <f t="shared" si="5"/>
-        <v>2125.6501317061625</v>
-      </c>
-    </row>
-    <row r="358" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="358" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A358">
         <v>363.940369207</v>
       </c>
@@ -10518,12 +8854,8 @@
       <c r="F358">
         <v>-1151.6920840732</v>
       </c>
-      <c r="H358">
-        <f t="shared" si="5"/>
-        <v>1292.6293445398405</v>
-      </c>
-    </row>
-    <row r="359" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="359" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A359">
         <v>383.10770522452901</v>
       </c>
@@ -10542,12 +8874,8 @@
       <c r="F359">
         <v>2819.7042365549601</v>
       </c>
-      <c r="H359">
-        <f t="shared" si="5"/>
-        <v>4999.9999999999982</v>
-      </c>
-    </row>
-    <row r="360" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="360" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A360">
         <v>406.99294219228898</v>
       </c>
@@ -10566,12 +8894,8 @@
       <c r="F360">
         <v>1119.8501381634801</v>
       </c>
-      <c r="H360">
-        <f t="shared" si="5"/>
-        <v>5000</v>
-      </c>
-    </row>
-    <row r="361" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="361" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A361">
         <v>411.50015087513498</v>
       </c>
@@ -10590,12 +8914,8 @@
       <c r="F361">
         <v>-4213.6547509007396</v>
       </c>
-      <c r="H361">
-        <f t="shared" si="5"/>
-        <v>1169.7085430296593</v>
-      </c>
-    </row>
-    <row r="362" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="362" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A362">
         <v>423.33241819839799</v>
       </c>
@@ -10614,12 +8934,8 @@
       <c r="F362">
         <v>391.862656336074</v>
       </c>
-      <c r="H362">
-        <f t="shared" si="5"/>
-        <v>894.26331305286988</v>
-      </c>
-    </row>
-    <row r="363" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="363" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A363">
         <v>445.69238211142698</v>
       </c>
@@ -10638,12 +8954,8 @@
       <c r="F363">
         <v>1792.9108859046801</v>
       </c>
-      <c r="H363">
-        <f t="shared" si="5"/>
-        <v>1016.608137004445</v>
-      </c>
-    </row>
-    <row r="364" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="364" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A364">
         <v>458.13412758555899</v>
       </c>
@@ -10662,12 +8974,8 @@
       <c r="F364">
         <v>-928.56268999721703</v>
       </c>
-      <c r="H364">
-        <f t="shared" si="5"/>
-        <v>3572.5613264547146</v>
-      </c>
-    </row>
-    <row r="365" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="365" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A365">
         <v>492.40213107125101</v>
       </c>
@@ -10686,12 +8994,8 @@
       <c r="F365">
         <v>3971.5268854492801</v>
       </c>
-      <c r="H365">
-        <f t="shared" si="5"/>
-        <v>4508.6447391116844</v>
-      </c>
-    </row>
-    <row r="366" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="366" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A366">
         <v>494.06862000113699</v>
       </c>
@@ -10710,12 +9014,8 @@
       <c r="F366">
         <v>705.74347297212705</v>
       </c>
-      <c r="H366">
-        <f t="shared" si="5"/>
-        <v>5000.0000000000036</v>
-      </c>
-    </row>
-    <row r="367" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="367" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A367">
         <v>496.85967896092501</v>
       </c>
@@ -10734,12 +9034,8 @@
       <c r="F367">
         <v>-5000</v>
       </c>
-      <c r="H367">
-        <f t="shared" si="5"/>
-        <v>1067.9300434311119</v>
-      </c>
-    </row>
-    <row r="368" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="368" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A368">
         <v>499.53842849983499</v>
       </c>
@@ -10758,12 +9054,8 @@
       <c r="F368">
         <v>-4677.1914213959099</v>
       </c>
-      <c r="H368">
-        <f t="shared" si="5"/>
-        <v>533.66128803094989</v>
-      </c>
-    </row>
-    <row r="369" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="369" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A369">
         <v>532.30864535584703</v>
       </c>
@@ -10782,12 +9074,8 @@
       <c r="F369">
         <v>3068.92103077088</v>
       </c>
-      <c r="H369">
-        <f t="shared" si="5"/>
-        <v>4503.3275416685874</v>
-      </c>
-    </row>
-    <row r="370" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="370" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A370">
         <v>550.79103634034698</v>
       </c>
@@ -10806,12 +9094,8 @@
       <c r="F370">
         <v>3116.9081074001901</v>
       </c>
-      <c r="H370">
-        <f t="shared" si="5"/>
-        <v>4105.7366869471271</v>
-      </c>
-    </row>
-    <row r="371" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="371" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A371">
         <v>559.91870832304005</v>
       </c>
@@ -10830,12 +9114,8 @@
       <c r="F371">
         <v>-801.18251477906006</v>
       </c>
-      <c r="H371">
-        <f t="shared" si="5"/>
-        <v>881.26272568309071</v>
-      </c>
-    </row>
-    <row r="372" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="372" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A372">
         <v>565.20973429724199</v>
       </c>
@@ -10854,12 +9134,8 @@
       <c r="F372">
         <v>-931.98573653858205</v>
       </c>
-      <c r="H372">
-        <f t="shared" si="5"/>
-        <v>5000.0000000000018</v>
-      </c>
-    </row>
-    <row r="373" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="373" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A373">
         <v>602.99394257361803</v>
       </c>
@@ -10878,12 +9154,8 @@
       <c r="F373">
         <v>-677.25774305579102</v>
       </c>
-      <c r="H373">
-        <f t="shared" si="5"/>
-        <v>1303.0903682485884</v>
-      </c>
-    </row>
-    <row r="374" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="374" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A374">
         <v>622.39851840567303</v>
       </c>
@@ -10902,12 +9174,8 @@
       <c r="F374">
         <v>-1861.96141984202</v>
       </c>
-      <c r="H374">
-        <f t="shared" si="5"/>
-        <v>4999.9999999999973</v>
-      </c>
-    </row>
-    <row r="375" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="375" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A375">
         <v>668.60470986221799</v>
       </c>
@@ -10926,12 +9194,8 @@
       <c r="F375">
         <v>-2575.85735602872</v>
       </c>
-      <c r="H375">
-        <f t="shared" si="5"/>
-        <v>5000.0000000000045</v>
-      </c>
-    </row>
-    <row r="376" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="376" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A376">
         <v>744.52383481445099</v>
       </c>
@@ -10950,12 +9214,8 @@
       <c r="F376">
         <v>-923.97059335965901</v>
       </c>
-      <c r="H376">
-        <f t="shared" si="5"/>
-        <v>4296.3421583707559</v>
-      </c>
-    </row>
-    <row r="377" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="377" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A377">
         <v>757.86012021593206</v>
       </c>
@@ -10974,12 +9234,8 @@
       <c r="F377">
         <v>-1435.58005570366</v>
       </c>
-      <c r="H377">
-        <f t="shared" si="5"/>
-        <v>911.49466313439564</v>
-      </c>
-    </row>
-    <row r="378" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="378" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A378">
         <v>778.80980571853502</v>
       </c>
@@ -10998,12 +9254,8 @@
       <c r="F378">
         <v>-3540.2606146195999</v>
       </c>
-      <c r="H378">
-        <f t="shared" si="5"/>
-        <v>1341.3685670014031</v>
-      </c>
-    </row>
-    <row r="379" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="379" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A379">
         <v>795.17892630339099</v>
       </c>
@@ -11022,12 +9274,8 @@
       <c r="F379">
         <v>-4185.5149028105398</v>
       </c>
-      <c r="H379">
-        <f t="shared" si="5"/>
-        <v>5000</v>
-      </c>
-    </row>
-    <row r="380" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="380" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A380">
         <v>806.51828442954604</v>
       </c>
@@ -11046,12 +9294,8 @@
       <c r="F380">
         <v>1997.3070581721499</v>
       </c>
-      <c r="H380">
-        <f t="shared" si="5"/>
-        <v>4541.6248776802677</v>
-      </c>
-    </row>
-    <row r="381" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="381" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A381">
         <v>865.06260761023702</v>
       </c>
@@ -11070,12 +9314,8 @@
       <c r="F381">
         <v>4837.3877241863502</v>
       </c>
-      <c r="H381">
-        <f t="shared" si="5"/>
-        <v>4999.9999999999991</v>
-      </c>
-    </row>
-    <row r="382" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="382" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A382">
         <v>944.76924703569705</v>
       </c>
@@ -11094,12 +9334,8 @@
       <c r="F382">
         <v>-1064.2890854585601</v>
       </c>
-      <c r="H382">
-        <f t="shared" si="5"/>
-        <v>5000.0000000000073</v>
-      </c>
-    </row>
-    <row r="383" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="383" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A383">
         <v>958.79203766628405</v>
       </c>
@@ -11118,12 +9354,8 @@
       <c r="F383">
         <v>-4442.8916691391496</v>
       </c>
-      <c r="H383">
-        <f t="shared" si="5"/>
-        <v>4168.3645462381928</v>
-      </c>
-    </row>
-    <row r="384" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="384" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A384">
         <v>985.10063092298401</v>
       </c>
@@ -11142,12 +9374,8 @@
       <c r="F384">
         <v>-4559.7396312110204</v>
       </c>
-      <c r="H384">
-        <f t="shared" si="5"/>
-        <v>4977.9654791387302</v>
-      </c>
-    </row>
-    <row r="385" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="385" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A385">
         <v>1001.72112666501</v>
       </c>
@@ -11166,12 +9394,8 @@
       <c r="F385">
         <v>3344.9959594328302</v>
       </c>
-      <c r="H385">
-        <f t="shared" si="5"/>
-        <v>1514.1331029984733</v>
-      </c>
-    </row>
-    <row r="386" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="386" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A386">
         <v>1002.39598117343</v>
       </c>
@@ -11190,12 +9414,8 @@
       <c r="F386">
         <v>3784.7454513590401</v>
       </c>
-      <c r="H386">
-        <f t="shared" si="5"/>
-        <v>5000.0000000000009</v>
-      </c>
-    </row>
-    <row r="387" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="387" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A387">
         <v>1005.10802619205</v>
       </c>
@@ -11214,12 +9434,8 @@
       <c r="F387">
         <v>2110.9736597309602</v>
       </c>
-      <c r="H387">
-        <f t="shared" si="5"/>
-        <v>5000</v>
-      </c>
-    </row>
-    <row r="388" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="388" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A388">
         <v>1012.94925318949</v>
       </c>
@@ -11238,12 +9454,8 @@
       <c r="F388">
         <v>-4333.0837098770899</v>
       </c>
-      <c r="H388">
-        <f t="shared" si="5"/>
-        <v>4309.288979133511</v>
-      </c>
-    </row>
-    <row r="389" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="389" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A389">
         <v>1023.47987152438</v>
       </c>
@@ -11262,12 +9474,8 @@
       <c r="F389">
         <v>-996.80909486701205</v>
       </c>
-      <c r="H389">
-        <f t="shared" ref="H389:H452" si="6">SQRT((D389-A389)^2+(E389-B389)^2+(F389-C389)^2)</f>
-        <v>5000</v>
-      </c>
-    </row>
-    <row r="390" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="390" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A390">
         <v>1034.7078292860999</v>
       </c>
@@ -11286,12 +9494,8 @@
       <c r="F390">
         <v>3838.8453645466602</v>
       </c>
-      <c r="H390">
-        <f t="shared" si="6"/>
-        <v>4080.5928834967062</v>
-      </c>
-    </row>
-    <row r="391" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="391" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A391">
         <v>1051.01118043376</v>
       </c>
@@ -11310,12 +9514,8 @@
       <c r="F391">
         <v>1046.14265670484</v>
       </c>
-      <c r="H391">
-        <f t="shared" si="6"/>
-        <v>4904.3010733655856</v>
-      </c>
-    </row>
-    <row r="392" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="392" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A392">
         <v>1071.59727602405</v>
       </c>
@@ -11334,12 +9534,8 @@
       <c r="F392">
         <v>2300.5927856599901</v>
       </c>
-      <c r="H392">
-        <f t="shared" si="6"/>
-        <v>4911.8701667117139</v>
-      </c>
-    </row>
-    <row r="393" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="393" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A393">
         <v>1092.3014322563799</v>
       </c>
@@ -11358,12 +9554,8 @@
       <c r="F393">
         <v>1772.19301561112</v>
       </c>
-      <c r="H393">
-        <f t="shared" si="6"/>
-        <v>3843.4971031974574</v>
-      </c>
-    </row>
-    <row r="394" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="394" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A394">
         <v>1120.5401339770599</v>
       </c>
@@ -11382,12 +9574,8 @@
       <c r="F394">
         <v>3535.0584121371098</v>
       </c>
-      <c r="H394">
-        <f t="shared" si="6"/>
-        <v>3485.8668970015251</v>
-      </c>
-    </row>
-    <row r="395" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="395" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A395">
         <v>1195.37898799255</v>
       </c>
@@ -11406,12 +9594,8 @@
       <c r="F395">
         <v>-2329.3610365355898</v>
       </c>
-      <c r="H395">
-        <f t="shared" si="6"/>
-        <v>4195.0974146995432</v>
-      </c>
-    </row>
-    <row r="396" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="396" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A396">
         <v>1264.7029821799799</v>
       </c>
@@ -11430,12 +9614,8 @@
       <c r="F396">
         <v>3912.4468166528</v>
       </c>
-      <c r="H396">
-        <f t="shared" si="6"/>
-        <v>5000.0000000000018</v>
-      </c>
-    </row>
-    <row r="397" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="397" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A397">
         <v>1272.6519282909301</v>
       </c>
@@ -11454,12 +9634,8 @@
       <c r="F397">
         <v>2373.3031723710201</v>
       </c>
-      <c r="H397">
-        <f t="shared" si="6"/>
-        <v>3932.0699565688828</v>
-      </c>
-    </row>
-    <row r="398" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="398" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A398">
         <v>1279.6763885325299</v>
       </c>
@@ -11478,12 +9654,8 @@
       <c r="F398">
         <v>5000</v>
       </c>
-      <c r="H398">
-        <f t="shared" si="6"/>
-        <v>4695.5411211253731</v>
-      </c>
-    </row>
-    <row r="399" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="399" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A399">
         <v>1292.7703805559199</v>
       </c>
@@ -11502,12 +9674,8 @@
       <c r="F399">
         <v>1530.2759915418601</v>
       </c>
-      <c r="H399">
-        <f t="shared" si="6"/>
-        <v>5000</v>
-      </c>
-    </row>
-    <row r="400" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="400" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A400">
         <v>1324.27827172855</v>
       </c>
@@ -11526,12 +9694,8 @@
       <c r="F400">
         <v>3668.5222494690702</v>
       </c>
-      <c r="H400">
-        <f t="shared" si="6"/>
-        <v>4018.6120237373934</v>
-      </c>
-    </row>
-    <row r="401" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="401" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A401">
         <v>1325.2276863621501</v>
       </c>
@@ -11550,12 +9714,8 @@
       <c r="F401">
         <v>-5000</v>
       </c>
-      <c r="H401">
-        <f t="shared" si="6"/>
-        <v>912.70474536474387</v>
-      </c>
-    </row>
-    <row r="402" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="402" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A402">
         <v>1351.8543590859799</v>
       </c>
@@ -11574,12 +9734,8 @@
       <c r="F402">
         <v>2696.2224591212298</v>
       </c>
-      <c r="H402">
-        <f t="shared" si="6"/>
-        <v>605.06817985278371</v>
-      </c>
-    </row>
-    <row r="403" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="403" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A403">
         <v>1388.2337937831401</v>
       </c>
@@ -11598,12 +9754,8 @@
       <c r="F403">
         <v>-5000</v>
       </c>
-      <c r="H403">
-        <f t="shared" si="6"/>
-        <v>1339.5226363770219</v>
-      </c>
-    </row>
-    <row r="404" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="404" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A404">
         <v>1390.0730900733799</v>
       </c>
@@ -11622,12 +9774,8 @@
       <c r="F404">
         <v>1855.54491806651</v>
       </c>
-      <c r="H404">
-        <f t="shared" si="6"/>
-        <v>3866.1251457989711</v>
-      </c>
-    </row>
-    <row r="405" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="405" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A405">
         <v>1419.93383280489</v>
       </c>
@@ -11646,12 +9794,8 @@
       <c r="F405">
         <v>-3930.2164159703898</v>
       </c>
-      <c r="H405">
-        <f t="shared" si="6"/>
-        <v>3777.4196606006167</v>
-      </c>
-    </row>
-    <row r="406" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="406" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A406">
         <v>1458.74307874793</v>
       </c>
@@ -11670,12 +9814,8 @@
       <c r="F406">
         <v>2970.1148623983599</v>
       </c>
-      <c r="H406">
-        <f t="shared" si="6"/>
-        <v>5000</v>
-      </c>
-    </row>
-    <row r="407" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="407" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A407">
         <v>1458.9009018706699</v>
       </c>
@@ -11694,12 +9834,8 @@
       <c r="F407">
         <v>3671.15804563146</v>
       </c>
-      <c r="H407">
-        <f t="shared" si="6"/>
-        <v>4999.9999999999927</v>
-      </c>
-    </row>
-    <row r="408" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="408" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A408">
         <v>1468.5101121479199</v>
       </c>
@@ -11718,12 +9854,8 @@
       <c r="F408">
         <v>-5000</v>
       </c>
-      <c r="H408">
-        <f t="shared" si="6"/>
-        <v>2058.3878031456779</v>
-      </c>
-    </row>
-    <row r="409" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="409" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A409">
         <v>1472.6308314686901</v>
       </c>
@@ -11742,12 +9874,8 @@
       <c r="F409">
         <v>4601.42214993779</v>
       </c>
-      <c r="H409">
-        <f t="shared" si="6"/>
-        <v>1370.5238648761085</v>
-      </c>
-    </row>
-    <row r="410" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="410" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A410">
         <v>1531.2117876557099</v>
       </c>
@@ -11766,12 +9894,8 @@
       <c r="F410">
         <v>-4377.6338925583204</v>
       </c>
-      <c r="H410">
-        <f t="shared" si="6"/>
-        <v>1726.9768992686998</v>
-      </c>
-    </row>
-    <row r="411" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="411" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A411">
         <v>1540.9007627081701</v>
       </c>
@@ -11790,12 +9914,8 @@
       <c r="F411">
         <v>-4326.0619514530899</v>
       </c>
-      <c r="H411">
-        <f t="shared" si="6"/>
-        <v>5000.0000000000027</v>
-      </c>
-    </row>
-    <row r="412" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="412" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A412">
         <v>1544.6530312542</v>
       </c>
@@ -11814,12 +9934,8 @@
       <c r="F412">
         <v>-1629.6217829257901</v>
       </c>
-      <c r="H412">
-        <f t="shared" si="6"/>
-        <v>4002.9978373003241</v>
-      </c>
-    </row>
-    <row r="413" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="413" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A413">
         <v>1549.1275958178201</v>
       </c>
@@ -11838,12 +9954,8 @@
       <c r="F413">
         <v>-400.65627383071302</v>
       </c>
-      <c r="H413">
-        <f t="shared" si="6"/>
-        <v>4555.103902983572</v>
-      </c>
-    </row>
-    <row r="414" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="414" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A414">
         <v>1558.9811111367701</v>
       </c>
@@ -11862,12 +9974,8 @@
       <c r="F414">
         <v>3935.45436516269</v>
       </c>
-      <c r="H414">
-        <f t="shared" si="6"/>
-        <v>2289.9534987468737</v>
-      </c>
-    </row>
-    <row r="415" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="415" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A415">
         <v>1574.93897247575</v>
       </c>
@@ -11886,12 +9994,8 @@
       <c r="F415">
         <v>-3320.0383721326998</v>
       </c>
-      <c r="H415">
-        <f t="shared" si="6"/>
-        <v>4639.9414997900885</v>
-      </c>
-    </row>
-    <row r="416" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="416" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A416">
         <v>1578.7283328475601</v>
       </c>
@@ -11910,12 +10014,8 @@
       <c r="F416">
         <v>4176.5383715405596</v>
       </c>
-      <c r="H416">
-        <f t="shared" si="6"/>
-        <v>1020.8169103383756</v>
-      </c>
-    </row>
-    <row r="417" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="417" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A417">
         <v>1592.19789573657</v>
       </c>
@@ -11934,12 +10034,8 @@
       <c r="F417">
         <v>-1612.3017445724699</v>
       </c>
-      <c r="H417">
-        <f t="shared" si="6"/>
-        <v>4517.0429991017891</v>
-      </c>
-    </row>
-    <row r="418" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="418" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A418">
         <v>1608.6274533512601</v>
       </c>
@@ -11958,12 +10054,8 @@
       <c r="F418">
         <v>2432.06024610751</v>
       </c>
-      <c r="H418">
-        <f t="shared" si="6"/>
-        <v>3478.7007852495617</v>
-      </c>
-    </row>
-    <row r="419" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="419" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A419">
         <v>1610.7693465908801</v>
       </c>
@@ -11982,12 +10074,8 @@
       <c r="F419">
         <v>2709.3985569418701</v>
       </c>
-      <c r="H419">
-        <f t="shared" si="6"/>
-        <v>1268.2949505511795</v>
-      </c>
-    </row>
-    <row r="420" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="420" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A420">
         <v>1610.86558347968</v>
       </c>
@@ -12006,12 +10094,8 @@
       <c r="F420">
         <v>-1896.43590640861</v>
       </c>
-      <c r="H420">
-        <f t="shared" si="6"/>
-        <v>3004.539008658553</v>
-      </c>
-    </row>
-    <row r="421" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="421" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A421">
         <v>1646.5781058286</v>
       </c>
@@ -12030,12 +10114,8 @@
       <c r="F421">
         <v>1.5221859663427E-2</v>
       </c>
-      <c r="H421">
-        <f t="shared" si="6"/>
-        <v>3429.289243541356</v>
-      </c>
-    </row>
-    <row r="422" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="422" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A422">
         <v>1677.1279358484301</v>
       </c>
@@ -12054,12 +10134,8 @@
       <c r="F422">
         <v>1257.7692630332399</v>
       </c>
-      <c r="H422">
-        <f t="shared" si="6"/>
-        <v>1926.2883456729442</v>
-      </c>
-    </row>
-    <row r="423" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="423" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A423">
         <v>1684.6297985026299</v>
       </c>
@@ -12078,12 +10154,8 @@
       <c r="F423">
         <v>-1497.9146312252899</v>
       </c>
-      <c r="H423">
-        <f t="shared" si="6"/>
-        <v>4634.8736174810811</v>
-      </c>
-    </row>
-    <row r="424" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="424" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A424">
         <v>1712.18261113632</v>
       </c>
@@ -12102,12 +10174,8 @@
       <c r="F424">
         <v>3929.7031967729199</v>
       </c>
-      <c r="H424">
-        <f t="shared" si="6"/>
-        <v>3405.3211489593505</v>
-      </c>
-    </row>
-    <row r="425" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="425" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A425">
         <v>1714.24096612677</v>
       </c>
@@ -12126,12 +10194,8 @@
       <c r="F425">
         <v>4224.96559863317</v>
       </c>
-      <c r="H425">
-        <f t="shared" si="6"/>
-        <v>565.05458784584209</v>
-      </c>
-    </row>
-    <row r="426" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="426" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A426">
         <v>1730.0577830437001</v>
       </c>
@@ -12150,12 +10214,8 @@
       <c r="F426">
         <v>77.308769258619407</v>
       </c>
-      <c r="H426">
-        <f t="shared" si="6"/>
-        <v>3550.2585214109627</v>
-      </c>
-    </row>
-    <row r="427" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="427" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A427">
         <v>1755.97322242223</v>
       </c>
@@ -12174,12 +10234,8 @@
       <c r="F427">
         <v>3369.9963393839698</v>
       </c>
-      <c r="H427">
-        <f t="shared" si="6"/>
-        <v>4394.9318201472097</v>
-      </c>
-    </row>
-    <row r="428" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="428" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A428">
         <v>1762.1290154216599</v>
       </c>
@@ -12198,12 +10254,8 @@
       <c r="F428">
         <v>-5000</v>
       </c>
-      <c r="H428">
-        <f t="shared" si="6"/>
-        <v>674.31920267302905</v>
-      </c>
-    </row>
-    <row r="429" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="429" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A429">
         <v>1828.82464848207</v>
       </c>
@@ -12222,12 +10274,8 @@
       <c r="F429">
         <v>-5000</v>
       </c>
-      <c r="H429">
-        <f t="shared" si="6"/>
-        <v>2670.3402218321976</v>
-      </c>
-    </row>
-    <row r="430" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="430" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A430">
         <v>1836.78620348649</v>
       </c>
@@ -12246,12 +10294,8 @@
       <c r="F430">
         <v>2791.9743207577599</v>
       </c>
-      <c r="H430">
-        <f t="shared" si="6"/>
-        <v>4438.281695188839</v>
-      </c>
-    </row>
-    <row r="431" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="431" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A431">
         <v>1840.3107732435899</v>
       </c>
@@ -12270,12 +10314,8 @@
       <c r="F431">
         <v>-355.33148004822402</v>
       </c>
-      <c r="H431">
-        <f t="shared" si="6"/>
-        <v>3164.971096801552</v>
-      </c>
-    </row>
-    <row r="432" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="432" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A432">
         <v>1906.7507103477501</v>
       </c>
@@ -12294,12 +10334,8 @@
       <c r="F432">
         <v>3223.8980692701102</v>
       </c>
-      <c r="H432">
-        <f t="shared" si="6"/>
-        <v>4999.9999999999991</v>
-      </c>
-    </row>
-    <row r="433" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="433" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A433">
         <v>1926.06627797377</v>
       </c>
@@ -12318,12 +10354,8 @@
       <c r="F433">
         <v>5000</v>
       </c>
-      <c r="H433">
-        <f t="shared" si="6"/>
-        <v>3738.1177334967947</v>
-      </c>
-    </row>
-    <row r="434" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="434" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A434">
         <v>1956.60636853448</v>
       </c>
@@ -12342,12 +10374,8 @@
       <c r="F434">
         <v>3110.9800266842299</v>
       </c>
-      <c r="H434">
-        <f t="shared" si="6"/>
-        <v>4434.9454121541603</v>
-      </c>
-    </row>
-    <row r="435" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="435" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A435">
         <v>1971.10566789727</v>
       </c>
@@ -12366,12 +10394,8 @@
       <c r="F435">
         <v>4805.6048605752503</v>
       </c>
-      <c r="H435">
-        <f t="shared" si="6"/>
-        <v>1018.0999987567513</v>
-      </c>
-    </row>
-    <row r="436" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="436" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A436">
         <v>1972.0353051397899</v>
       </c>
@@ -12390,12 +10414,8 @@
       <c r="F436">
         <v>2189.4151926991099</v>
       </c>
-      <c r="H436">
-        <f t="shared" si="6"/>
-        <v>4087.2952546352626</v>
-      </c>
-    </row>
-    <row r="437" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="437" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A437">
         <v>2138.1518299695199</v>
       </c>
@@ -12414,12 +10434,8 @@
       <c r="F437">
         <v>-4722.9600227903802</v>
       </c>
-      <c r="H437">
-        <f t="shared" si="6"/>
-        <v>3392.2027637351389</v>
-      </c>
-    </row>
-    <row r="438" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="438" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A438">
         <v>2157.93527938752</v>
       </c>
@@ -12438,12 +10454,8 @@
       <c r="F438">
         <v>-4595.2639889585398</v>
       </c>
-      <c r="H438">
-        <f t="shared" si="6"/>
-        <v>4694.6036011640308</v>
-      </c>
-    </row>
-    <row r="439" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="439" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A439">
         <v>2185.9855598441</v>
       </c>
@@ -12462,12 +10474,8 @@
       <c r="F439">
         <v>4983.9849905990804</v>
       </c>
-      <c r="H439">
-        <f t="shared" si="6"/>
-        <v>4999.9999999999991</v>
-      </c>
-    </row>
-    <row r="440" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="440" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A440">
         <v>2194.7530985693502</v>
       </c>
@@ -12486,12 +10494,8 @@
       <c r="F440">
         <v>106.129939832887</v>
       </c>
-      <c r="H440">
-        <f t="shared" si="6"/>
-        <v>644.708591127967</v>
-      </c>
-    </row>
-    <row r="441" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="441" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A441">
         <v>2205.66157082781</v>
       </c>
@@ -12510,12 +10514,8 @@
       <c r="F441">
         <v>4070.0899397143498</v>
       </c>
-      <c r="H441">
-        <f t="shared" si="6"/>
-        <v>3731.7050494488185</v>
-      </c>
-    </row>
-    <row r="442" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="442" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A442">
         <v>2221.45452106537</v>
       </c>
@@ -12534,12 +10534,8 @@
       <c r="F442">
         <v>-5000</v>
       </c>
-      <c r="H442">
-        <f t="shared" si="6"/>
-        <v>656.61288014949537</v>
-      </c>
-    </row>
-    <row r="443" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="443" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A443">
         <v>2259.19601857106</v>
       </c>
@@ -12558,12 +10554,8 @@
       <c r="F443">
         <v>3287.08706342088</v>
       </c>
-      <c r="H443">
-        <f t="shared" si="6"/>
-        <v>4085.2967098994231</v>
-      </c>
-    </row>
-    <row r="444" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="444" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A444">
         <v>2265.94857369379</v>
       </c>
@@ -12582,12 +10574,8 @@
       <c r="F444">
         <v>-3453.8246948549699</v>
       </c>
-      <c r="H444">
-        <f t="shared" si="6"/>
-        <v>1140.0273176619794</v>
-      </c>
-    </row>
-    <row r="445" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="445" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A445">
         <v>2286.94509947694</v>
       </c>
@@ -12606,12 +10594,8 @@
       <c r="F445">
         <v>2206.8250848974399</v>
       </c>
-      <c r="H445">
-        <f t="shared" si="6"/>
-        <v>3159.5396150367401</v>
-      </c>
-    </row>
-    <row r="446" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="446" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A446">
         <v>2293.03898663167</v>
       </c>
@@ -12630,12 +10614,8 @@
       <c r="F446">
         <v>2524.2059780139102</v>
       </c>
-      <c r="H446">
-        <f t="shared" si="6"/>
-        <v>3948.0664498140163</v>
-      </c>
-    </row>
-    <row r="447" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="447" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A447">
         <v>2308.2110444853402</v>
       </c>
@@ -12654,12 +10634,8 @@
       <c r="F447">
         <v>3156.6251601283702</v>
       </c>
-      <c r="H447">
-        <f t="shared" si="6"/>
-        <v>3323.9053578799403</v>
-      </c>
-    </row>
-    <row r="448" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="448" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A448">
         <v>2349.5142277396599</v>
       </c>
@@ -12678,12 +10654,8 @@
       <c r="F448">
         <v>-2375.9813515493502</v>
       </c>
-      <c r="H448">
-        <f t="shared" si="6"/>
-        <v>5000</v>
-      </c>
-    </row>
-    <row r="449" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="449" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A449">
         <v>2363.5092257295901</v>
       </c>
@@ -12702,12 +10674,8 @@
       <c r="F449">
         <v>-3530.3019787493699</v>
       </c>
-      <c r="H449">
-        <f t="shared" si="6"/>
-        <v>2649.4309333865003</v>
-      </c>
-    </row>
-    <row r="450" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="450" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A450">
         <v>2389.1003916356999</v>
       </c>
@@ -12726,12 +10694,8 @@
       <c r="F450">
         <v>2617.2585401956399</v>
       </c>
-      <c r="H450">
-        <f t="shared" si="6"/>
-        <v>2941.6121968543225</v>
-      </c>
-    </row>
-    <row r="451" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="451" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A451">
         <v>2402.44476182982</v>
       </c>
@@ -12750,12 +10714,8 @@
       <c r="F451">
         <v>-1609.38371949568</v>
       </c>
-      <c r="H451">
-        <f t="shared" si="6"/>
-        <v>4129.5726162514948</v>
-      </c>
-    </row>
-    <row r="452" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="452" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A452">
         <v>2514.5256262734802</v>
       </c>
@@ -12774,12 +10734,8 @@
       <c r="F452">
         <v>-2547.29172280084</v>
       </c>
-      <c r="H452">
-        <f t="shared" si="6"/>
-        <v>2502.8717515086646</v>
-      </c>
-    </row>
-    <row r="453" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="453" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A453">
         <v>2517.4694339469102</v>
       </c>
@@ -12798,12 +10754,8 @@
       <c r="F453">
         <v>-5000</v>
       </c>
-      <c r="H453">
-        <f t="shared" ref="H453:H516" si="7">SQRT((D453-A453)^2+(E453-B453)^2+(F453-C453)^2)</f>
-        <v>4102.1219755847451</v>
-      </c>
-    </row>
-    <row r="454" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="454" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A454">
         <v>2519.42483136072</v>
       </c>
@@ -12822,12 +10774,8 @@
       <c r="F454">
         <v>396.82717551722402</v>
       </c>
-      <c r="H454">
-        <f t="shared" si="7"/>
-        <v>2502.4017236216232</v>
-      </c>
-    </row>
-    <row r="455" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="455" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A455">
         <v>2528.2160669588102</v>
       </c>
@@ -12846,12 +10794,8 @@
       <c r="F455">
         <v>-1847.27905913323</v>
       </c>
-      <c r="H455">
-        <f t="shared" si="7"/>
-        <v>4999.9999999999955</v>
-      </c>
-    </row>
-    <row r="456" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="456" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A456">
         <v>2539.6914001314599</v>
       </c>
@@ -12870,12 +10814,8 @@
       <c r="F456">
         <v>3782.5961693674299</v>
       </c>
-      <c r="H456">
-        <f t="shared" si="7"/>
-        <v>2782.1878034516976</v>
-      </c>
-    </row>
-    <row r="457" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="457" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A457">
         <v>2560.6744544560302</v>
       </c>
@@ -12894,12 +10834,8 @@
       <c r="F457">
         <v>3732.7090860406302</v>
       </c>
-      <c r="H457">
-        <f t="shared" si="7"/>
-        <v>3440.2476629855578</v>
-      </c>
-    </row>
-    <row r="458" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="458" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A458">
         <v>2572.7360312594301</v>
       </c>
@@ -12918,12 +10854,8 @@
       <c r="F458">
         <v>2439.6063980396202</v>
       </c>
-      <c r="H458">
-        <f t="shared" si="7"/>
-        <v>2502.1590553949318</v>
-      </c>
-    </row>
-    <row r="459" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="459" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A459">
         <v>2599.8480857828499</v>
       </c>
@@ -12942,12 +10874,8 @@
       <c r="F459">
         <v>-993.41459346892896</v>
       </c>
-      <c r="H459">
-        <f t="shared" si="7"/>
-        <v>3859.9726823380142</v>
-      </c>
-    </row>
-    <row r="460" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="460" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A460">
         <v>2644.7688768849998</v>
       </c>
@@ -12966,12 +10894,8 @@
       <c r="F460">
         <v>3119.91228873309</v>
       </c>
-      <c r="H460">
-        <f t="shared" si="7"/>
-        <v>2329.6597781678006</v>
-      </c>
-    </row>
-    <row r="461" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="461" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A461">
         <v>2660.2022599724401</v>
       </c>
@@ -12990,12 +10914,8 @@
       <c r="F461">
         <v>-2132.46832683517</v>
       </c>
-      <c r="H461">
-        <f t="shared" si="7"/>
-        <v>4188.0327594349874</v>
-      </c>
-    </row>
-    <row r="462" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="462" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A462">
         <v>2667.1155165574301</v>
       </c>
@@ -13014,12 +10934,8 @@
       <c r="F462">
         <v>1997.53543006836</v>
       </c>
-      <c r="H462">
-        <f t="shared" si="7"/>
-        <v>4999.9999999999973</v>
-      </c>
-    </row>
-    <row r="463" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="463" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A463">
         <v>2685.69369049022</v>
       </c>
@@ -13038,12 +10954,8 @@
       <c r="F463">
         <v>1139.4770881954801</v>
       </c>
-      <c r="H463">
-        <f t="shared" si="7"/>
-        <v>2314.3239712419031</v>
-      </c>
-    </row>
-    <row r="464" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="464" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A464">
         <v>2697.4678506611199</v>
       </c>
@@ -13062,12 +10974,8 @@
       <c r="F464">
         <v>288.90164227430301</v>
       </c>
-      <c r="H464">
-        <f t="shared" si="7"/>
-        <v>3528.7768458041041</v>
-      </c>
-    </row>
-    <row r="465" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="465" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A465">
         <v>2729.3471989638701</v>
       </c>
@@ -13086,12 +10994,8 @@
       <c r="F465">
         <v>200.799658762158</v>
       </c>
-      <c r="H465">
-        <f t="shared" si="7"/>
-        <v>2424.2247040411748</v>
-      </c>
-    </row>
-    <row r="466" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="466" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A466">
         <v>2739.0051033601198</v>
       </c>
@@ -13110,12 +11014,8 @@
       <c r="F466">
         <v>-1294.2392002071899</v>
       </c>
-      <c r="H466">
-        <f t="shared" si="7"/>
-        <v>2694.2257957881316</v>
-      </c>
-    </row>
-    <row r="467" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="467" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A467">
         <v>2749.7099488747499</v>
       </c>
@@ -13134,12 +11034,8 @@
       <c r="F467">
         <v>4543.3080838598798</v>
       </c>
-      <c r="H467">
-        <f t="shared" si="7"/>
-        <v>1478.2002368731789</v>
-      </c>
-    </row>
-    <row r="468" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="468" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A468">
         <v>2758.8885769766098</v>
       </c>
@@ -13158,12 +11054,8 @@
       <c r="F468">
         <v>-1448.8507058391899</v>
       </c>
-      <c r="H468">
-        <f t="shared" si="7"/>
-        <v>2280.3960936551271</v>
-      </c>
-    </row>
-    <row r="469" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="469" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A469">
         <v>2788.0763958673501</v>
       </c>
@@ -13182,12 +11074,8 @@
       <c r="F469">
         <v>-3859.5185067499401</v>
       </c>
-      <c r="H469">
-        <f t="shared" si="7"/>
-        <v>4353.8720748126725</v>
-      </c>
-    </row>
-    <row r="470" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="470" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A470">
         <v>2791.90602670714</v>
       </c>
@@ -13206,12 +11094,8 @@
       <c r="F470">
         <v>-3564.5035417723302</v>
       </c>
-      <c r="H470">
-        <f t="shared" si="7"/>
-        <v>5000.0000000000018</v>
-      </c>
-    </row>
-    <row r="471" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="471" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A471">
         <v>2811.3572892314501</v>
       </c>
@@ -13230,12 +11114,8 @@
       <c r="F471">
         <v>-422.15680427322201</v>
       </c>
-      <c r="H471">
-        <f t="shared" si="7"/>
-        <v>2288.3995598974711</v>
-      </c>
-    </row>
-    <row r="472" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="472" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A472">
         <v>2842.0893141085198</v>
       </c>
@@ -13254,12 +11134,8 @@
       <c r="F472">
         <v>4316.19087821228</v>
       </c>
-      <c r="H472">
-        <f t="shared" si="7"/>
-        <v>2283.0043794693738</v>
-      </c>
-    </row>
-    <row r="473" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="473" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A473">
         <v>2927.5774530720601</v>
       </c>
@@ -13278,12 +11154,8 @@
       <c r="F473">
         <v>4449.6097810615602</v>
       </c>
-      <c r="H473">
-        <f t="shared" si="7"/>
-        <v>2437.3543625018033</v>
-      </c>
-    </row>
-    <row r="474" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="474" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A474">
         <v>2961.5933683308699</v>
       </c>
@@ -13302,12 +11174,8 @@
       <c r="F474">
         <v>933.89190657159702</v>
       </c>
-      <c r="H474">
-        <f t="shared" si="7"/>
-        <v>3833.5310053282133</v>
-      </c>
-    </row>
-    <row r="475" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="475" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A475">
         <v>2974.9158119998101</v>
       </c>
@@ -13326,12 +11194,8 @@
       <c r="F475">
         <v>-2721.1212254749198</v>
       </c>
-      <c r="H475">
-        <f t="shared" si="7"/>
-        <v>1894.7135346389393</v>
-      </c>
-    </row>
-    <row r="476" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="476" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A476">
         <v>3008.2048228710601</v>
       </c>
@@ -13350,12 +11214,8 @@
       <c r="F476">
         <v>-1569.8280618091501</v>
       </c>
-      <c r="H476">
-        <f t="shared" si="7"/>
-        <v>939.722531126788</v>
-      </c>
-    </row>
-    <row r="477" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="477" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A477">
         <v>3077.34290090167</v>
       </c>
@@ -13374,12 +11234,8 @@
       <c r="F477">
         <v>4222.6084986813803</v>
       </c>
-      <c r="H477">
-        <f t="shared" si="7"/>
-        <v>897.87802441525082</v>
-      </c>
-    </row>
-    <row r="478" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="478" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A478">
         <v>3130.0560128457701</v>
       </c>
@@ -13398,12 +11254,8 @@
       <c r="F478">
         <v>-1116.3352324227101</v>
       </c>
-      <c r="H478">
-        <f t="shared" si="7"/>
-        <v>4632.089965435156</v>
-      </c>
-    </row>
-    <row r="479" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="479" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A479">
         <v>3211.3428795915102</v>
       </c>
@@ -13422,12 +11274,8 @@
       <c r="F479">
         <v>-1126.5532918583699</v>
       </c>
-      <c r="H479">
-        <f t="shared" si="7"/>
-        <v>1808.2593394985577</v>
-      </c>
-    </row>
-    <row r="480" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="480" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A480">
         <v>3254.1939952448702</v>
       </c>
@@ -13446,12 +11294,8 @@
       <c r="F480">
         <v>-2260.4802700898499</v>
       </c>
-      <c r="H480">
-        <f t="shared" si="7"/>
-        <v>2118.5863119060564</v>
-      </c>
-    </row>
-    <row r="481" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="481" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A481">
         <v>3332.2659775617599</v>
       </c>
@@ -13470,12 +11314,8 @@
       <c r="F481">
         <v>-1252.26830164535</v>
       </c>
-      <c r="H481">
-        <f t="shared" si="7"/>
-        <v>1887.0545979477754</v>
-      </c>
-    </row>
-    <row r="482" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="482" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A482">
         <v>3349.07042751365</v>
       </c>
@@ -13494,12 +11334,8 @@
       <c r="F482">
         <v>2880.1455566300001</v>
       </c>
-      <c r="H482">
-        <f t="shared" si="7"/>
-        <v>2234.7119381515931</v>
-      </c>
-    </row>
-    <row r="483" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="483" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A483">
         <v>3365.0337262746398</v>
       </c>
@@ -13518,12 +11354,8 @@
       <c r="F483">
         <v>4019.8470874478899</v>
       </c>
-      <c r="H483">
-        <f t="shared" si="7"/>
-        <v>1923.2125430142432</v>
-      </c>
-    </row>
-    <row r="484" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="484" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A484">
         <v>3381.8554278649299</v>
       </c>
@@ -13542,12 +11374,8 @@
       <c r="F484">
         <v>-712.47056306405705</v>
       </c>
-      <c r="H484">
-        <f t="shared" si="7"/>
-        <v>1897.5950308470324</v>
-      </c>
-    </row>
-    <row r="485" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="485" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A485">
         <v>3389.2206878915299</v>
       </c>
@@ -13566,12 +11394,8 @@
       <c r="F485">
         <v>5000</v>
       </c>
-      <c r="H485">
-        <f t="shared" si="7"/>
-        <v>4630.1782469582176</v>
-      </c>
-    </row>
-    <row r="486" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="486" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A486">
         <v>3396.6972244722901</v>
       </c>
@@ -13590,12 +11414,8 @@
       <c r="F486">
         <v>-552.43859676401701</v>
       </c>
-      <c r="H486">
-        <f t="shared" si="7"/>
-        <v>4999.9999999999991</v>
-      </c>
-    </row>
-    <row r="487" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="487" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A487">
         <v>3442.3024922107702</v>
       </c>
@@ -13614,12 +11434,8 @@
       <c r="F487">
         <v>3025.3156501817798</v>
       </c>
-      <c r="H487">
-        <f t="shared" si="7"/>
-        <v>1557.9075663505832</v>
-      </c>
-    </row>
-    <row r="488" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="488" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A488">
         <v>3462.7759972037102</v>
       </c>
@@ -13638,12 +11454,8 @@
       <c r="F488">
         <v>-3244.9623980885099</v>
       </c>
-      <c r="H488">
-        <f t="shared" si="7"/>
-        <v>3177.8610531944323</v>
-      </c>
-    </row>
-    <row r="489" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="489" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A489">
         <v>3465.1858346485201</v>
       </c>
@@ -13662,12 +11474,8 @@
       <c r="F489">
         <v>-585.49279551162897</v>
       </c>
-      <c r="H489">
-        <f t="shared" si="7"/>
-        <v>5000.0000000000018</v>
-      </c>
-    </row>
-    <row r="490" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="490" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A490">
         <v>3494.54286652056</v>
       </c>
@@ -13686,12 +11494,8 @@
       <c r="F490">
         <v>964.35966645430904</v>
       </c>
-      <c r="H490">
-        <f t="shared" si="7"/>
-        <v>1595.64251519556</v>
-      </c>
-    </row>
-    <row r="491" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="491" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A491">
         <v>3509.60898672962</v>
       </c>
@@ -13710,12 +11514,8 @@
       <c r="F491">
         <v>-2351.8855380324499</v>
       </c>
-      <c r="H491">
-        <f t="shared" si="7"/>
-        <v>1673.9469748498759</v>
-      </c>
-    </row>
-    <row r="492" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="492" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A492">
         <v>3512.8759241001198</v>
       </c>
@@ -13734,12 +11534,8 @@
       <c r="F492">
         <v>923.476102249517</v>
       </c>
-      <c r="H492">
-        <f t="shared" si="7"/>
-        <v>1490.0694209549522</v>
-      </c>
-    </row>
-    <row r="493" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="493" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A493">
         <v>3529.5230270248699</v>
       </c>
@@ -13758,12 +11554,8 @@
       <c r="F493">
         <v>-1584.9029094725299</v>
       </c>
-      <c r="H493">
-        <f t="shared" si="7"/>
-        <v>1567.7440851839326</v>
-      </c>
-    </row>
-    <row r="494" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="494" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A494">
         <v>3577.9456722321502</v>
       </c>
@@ -13782,12 +11574,8 @@
       <c r="F494">
         <v>5000</v>
       </c>
-      <c r="H494">
-        <f t="shared" si="7"/>
-        <v>1086.3789717185155</v>
-      </c>
-    </row>
-    <row r="495" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="495" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A495">
         <v>3585.0777996440702</v>
       </c>
@@ -13806,12 +11594,8 @@
       <c r="F495">
         <v>-2888.1379645309398</v>
       </c>
-      <c r="H495">
-        <f t="shared" si="7"/>
-        <v>3105.2864653610682</v>
-      </c>
-    </row>
-    <row r="496" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="496" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A496">
         <v>3594.7081327476399</v>
       </c>
@@ -13830,12 +11614,8 @@
       <c r="F496">
         <v>-1130.46131818393</v>
       </c>
-      <c r="H496">
-        <f t="shared" si="7"/>
-        <v>3913.6210282814882</v>
-      </c>
-    </row>
-    <row r="497" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="497" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A497">
         <v>3618.8265370703198</v>
       </c>
@@ -13854,12 +11634,8 @@
       <c r="F497">
         <v>-4012.0695623134002</v>
       </c>
-      <c r="H497">
-        <f t="shared" si="7"/>
-        <v>646.12792518732601</v>
-      </c>
-    </row>
-    <row r="498" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="498" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A498">
         <v>3629.0204802408998</v>
       </c>
@@ -13878,12 +11654,8 @@
       <c r="F498">
         <v>-4734.5766871702599</v>
       </c>
-      <c r="H498">
-        <f t="shared" si="7"/>
-        <v>1512.8927458772378</v>
-      </c>
-    </row>
-    <row r="499" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="499" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A499">
         <v>3708.8196396195299</v>
       </c>
@@ -13902,12 +11674,8 @@
       <c r="F499">
         <v>1788.5618964415901</v>
       </c>
-      <c r="H499">
-        <f t="shared" si="7"/>
-        <v>1649.9399333492845</v>
-      </c>
-    </row>
-    <row r="500" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="500" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A500">
         <v>3834.6229365540298</v>
       </c>
@@ -13926,12 +11694,8 @@
       <c r="F500">
         <v>2438.90343590154</v>
       </c>
-      <c r="H500">
-        <f t="shared" si="7"/>
-        <v>1209.4882364858133</v>
-      </c>
-    </row>
-    <row r="501" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="501" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A501">
         <v>3864.2852027375802</v>
       </c>
@@ -13950,12 +11714,8 @@
       <c r="F501">
         <v>-447.70637422029802</v>
       </c>
-      <c r="H501">
-        <f t="shared" si="7"/>
-        <v>1148.5873328315261</v>
-      </c>
-    </row>
-    <row r="502" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="502" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A502">
         <v>3871.6249187009298</v>
       </c>
@@ -13974,12 +11734,8 @@
       <c r="F502">
         <v>-3645.7677697566901</v>
       </c>
-      <c r="H502">
-        <f t="shared" si="7"/>
-        <v>1639.9534796227301</v>
-      </c>
-    </row>
-    <row r="503" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="503" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A503">
         <v>3872.1625000004501</v>
       </c>
@@ -13998,12 +11754,8 @@
       <c r="F503">
         <v>1899.31110932199</v>
       </c>
-      <c r="H503">
-        <f t="shared" si="7"/>
-        <v>1600.1422819596492</v>
-      </c>
-    </row>
-    <row r="504" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="504" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A504">
         <v>3888.7455107248402</v>
       </c>
@@ -14022,12 +11774,8 @@
       <c r="F504">
         <v>1547.3999340221701</v>
       </c>
-      <c r="H504">
-        <f t="shared" si="7"/>
-        <v>1141.4659969434003</v>
-      </c>
-    </row>
-    <row r="505" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="505" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A505">
         <v>3907.2477493229999</v>
       </c>
@@ -14046,12 +11794,8 @@
       <c r="F505">
         <v>-4039.0450527108701</v>
       </c>
-      <c r="H505">
-        <f t="shared" si="7"/>
-        <v>1181.6163366639175</v>
-      </c>
-    </row>
-    <row r="506" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="506" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A506">
         <v>3941.9785699714598</v>
       </c>
@@ -14070,12 +11814,8 @@
       <c r="F506">
         <v>4304.4731721529497</v>
       </c>
-      <c r="H506">
-        <f t="shared" si="7"/>
-        <v>1288.4445725997384</v>
-      </c>
-    </row>
-    <row r="507" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="507" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A507">
         <v>3965.3355994048202</v>
       </c>
@@ -14094,12 +11834,8 @@
       <c r="F507">
         <v>-1349.0169894072501</v>
       </c>
-      <c r="H507">
-        <f t="shared" si="7"/>
-        <v>1463.4585628563148</v>
-      </c>
-    </row>
-    <row r="508" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="508" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A508">
         <v>3966.5998751551201</v>
       </c>
@@ -14118,12 +11854,8 @@
       <c r="F508">
         <v>1083.3790173988</v>
       </c>
-      <c r="H508">
-        <f t="shared" si="7"/>
-        <v>1034.2750195295882</v>
-      </c>
-    </row>
-    <row r="509" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="509" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A509">
         <v>3997.3300553951799</v>
       </c>
@@ -14142,12 +11874,8 @@
       <c r="F509">
         <v>3843.6487644506901</v>
       </c>
-      <c r="H509">
-        <f t="shared" si="7"/>
-        <v>1031.1063301677618</v>
-      </c>
-    </row>
-    <row r="510" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="510" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A510">
         <v>4007.6243465625398</v>
       </c>
@@ -14166,12 +11894,8 @@
       <c r="F510">
         <v>2473.3710616490098</v>
       </c>
-      <c r="H510">
-        <f t="shared" si="7"/>
-        <v>1571.8276675395848</v>
-      </c>
-    </row>
-    <row r="511" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="511" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A511">
         <v>4021.4000605306301</v>
       </c>
@@ -14190,12 +11914,8 @@
       <c r="F511">
         <v>2589.6427585873998</v>
       </c>
-      <c r="H511">
-        <f t="shared" si="7"/>
-        <v>1065.5302950763171</v>
-      </c>
-    </row>
-    <row r="512" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="512" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A512">
         <v>4049.4694770771498</v>
       </c>
@@ -14214,12 +11934,8 @@
       <c r="F512">
         <v>-3572.3942858098299</v>
       </c>
-      <c r="H512">
-        <f t="shared" si="7"/>
-        <v>2091.0662606991473</v>
-      </c>
-    </row>
-    <row r="513" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="513" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A513">
         <v>4091.8460826307701</v>
       </c>
@@ -14238,12 +11954,8 @@
       <c r="F513">
         <v>-3598.0044962676802</v>
       </c>
-      <c r="H513">
-        <f t="shared" si="7"/>
-        <v>1308.6446412901114</v>
-      </c>
-    </row>
-    <row r="514" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="514" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A514">
         <v>4116.00215602141</v>
       </c>
@@ -14262,12 +11974,8 @@
       <c r="F514">
         <v>3104.2146599304701</v>
       </c>
-      <c r="H514">
-        <f t="shared" si="7"/>
-        <v>963.46335605789989</v>
-      </c>
-    </row>
-    <row r="515" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="515" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A515">
         <v>4116.2035373632898</v>
       </c>
@@ -14286,12 +11994,8 @@
       <c r="F515">
         <v>-3977.3983679146399</v>
       </c>
-      <c r="H515">
-        <f t="shared" si="7"/>
-        <v>1261.8822665031953</v>
-      </c>
-    </row>
-    <row r="516" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="516" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A516">
         <v>4117.8861574476005</v>
       </c>
@@ -14310,12 +12014,8 @@
       <c r="F516">
         <v>-3937.3783635805798</v>
       </c>
-      <c r="H516">
-        <f t="shared" si="7"/>
-        <v>911.29201608982214</v>
-      </c>
-    </row>
-    <row r="517" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="517" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A517">
         <v>4193.6445164227098</v>
       </c>
@@ -14334,12 +12034,8 @@
       <c r="F517">
         <v>1730.2619455763199</v>
       </c>
-      <c r="H517">
-        <f t="shared" ref="H517:H537" si="8">SQRT((D517-A517)^2+(E517-B517)^2+(F517-C517)^2)</f>
-        <v>1274.2089133418469</v>
-      </c>
-    </row>
-    <row r="518" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="518" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A518">
         <v>4203.7327761217703</v>
       </c>
@@ -14358,12 +12054,8 @@
       <c r="F518">
         <v>-3498.0072623238202</v>
       </c>
-      <c r="H518">
-        <f t="shared" si="8"/>
-        <v>806.48153151757356</v>
-      </c>
-    </row>
-    <row r="519" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="519" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A519">
         <v>4207.5945219733003</v>
       </c>
@@ -14382,12 +12074,8 @@
       <c r="F519">
         <v>450.99467471885498</v>
       </c>
-      <c r="H519">
-        <f t="shared" si="8"/>
-        <v>907.50969412169525</v>
-      </c>
-    </row>
-    <row r="520" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="520" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A520">
         <v>4219.8800986775796</v>
       </c>
@@ -14406,12 +12094,8 @@
       <c r="F520">
         <v>5000</v>
       </c>
-      <c r="H520">
-        <f t="shared" si="8"/>
-        <v>584.98632715528618</v>
-      </c>
-    </row>
-    <row r="521" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="521" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A521">
         <v>4264.9194451070098</v>
       </c>
@@ -14430,12 +12114,8 @@
       <c r="F521">
         <v>-3256.3901885424998</v>
       </c>
-      <c r="H521">
-        <f t="shared" si="8"/>
-        <v>911.96979727254723</v>
-      </c>
-    </row>
-    <row r="522" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="522" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A522">
         <v>4282.8713881886397</v>
       </c>
@@ -14454,12 +12134,8 @@
       <c r="F522">
         <v>-1330.47391306341</v>
       </c>
-      <c r="H522">
-        <f t="shared" si="8"/>
-        <v>1549.9560399432416</v>
-      </c>
-    </row>
-    <row r="523" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="523" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A523">
         <v>4290.8768048778602</v>
       </c>
@@ -14478,12 +12154,8 @@
       <c r="F523">
         <v>-3042.6385211019401</v>
       </c>
-      <c r="H523">
-        <f t="shared" si="8"/>
-        <v>1334.3157331742616</v>
-      </c>
-    </row>
-    <row r="524" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="524" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A524">
         <v>4299.79896780538</v>
       </c>
@@ -14502,12 +12174,8 @@
       <c r="F524">
         <v>2353.8616724643898</v>
       </c>
-      <c r="H524">
-        <f t="shared" si="8"/>
-        <v>1136.354228690524</v>
-      </c>
-    </row>
-    <row r="525" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="525" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A525">
         <v>4321.6425499226298</v>
       </c>
@@ -14526,12 +12194,8 @@
       <c r="F525">
         <v>378.700572215921</v>
       </c>
-      <c r="H525">
-        <f t="shared" si="8"/>
-        <v>679.33513476608346</v>
-      </c>
-    </row>
-    <row r="526" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="526" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A526">
         <v>4325.2016342642401</v>
       </c>
@@ -14550,12 +12214,8 @@
       <c r="F526">
         <v>-1483.19311457291</v>
       </c>
-      <c r="H526">
-        <f t="shared" si="8"/>
-        <v>2784.2751274499942</v>
-      </c>
-    </row>
-    <row r="527" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="527" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A527">
         <v>4357.5171107679798</v>
       </c>
@@ -14574,12 +12234,8 @@
       <c r="F527">
         <v>1282.3086309167199</v>
       </c>
-      <c r="H527">
-        <f t="shared" si="8"/>
-        <v>657.81877812127595</v>
-      </c>
-    </row>
-    <row r="528" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="528" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A528">
         <v>4407.7330623889002</v>
       </c>
@@ -14598,12 +12254,8 @@
       <c r="F528">
         <v>2912.4304184525699</v>
       </c>
-      <c r="H528">
-        <f t="shared" si="8"/>
-        <v>616.1163991037306</v>
-      </c>
-    </row>
-    <row r="529" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="529" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A529">
         <v>4430.1109884059697</v>
       </c>
@@ -14622,12 +12274,8 @@
       <c r="F529">
         <v>127.577383940598</v>
       </c>
-      <c r="H529">
-        <f t="shared" si="8"/>
-        <v>749.33831513098471</v>
-      </c>
-    </row>
-    <row r="530" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="530" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A530">
         <v>4446.1856148013603</v>
       </c>
@@ -14646,12 +12294,8 @@
       <c r="F530">
         <v>4747.8430916557299</v>
       </c>
-      <c r="H530">
-        <f t="shared" si="8"/>
-        <v>608.78430405511801</v>
-      </c>
-    </row>
-    <row r="531" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="531" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A531">
         <v>4472.37546899875</v>
       </c>
@@ -14670,12 +12314,8 @@
       <c r="F531">
         <v>290.68323567421203</v>
       </c>
-      <c r="H531">
-        <f t="shared" si="8"/>
-        <v>1722.1376649752563</v>
-      </c>
-    </row>
-    <row r="532" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="532" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A532">
         <v>4484.2193071035999</v>
       </c>
@@ -14694,12 +12334,8 @@
       <c r="F532">
         <v>2224.3820222279401</v>
       </c>
-      <c r="H532">
-        <f t="shared" si="8"/>
-        <v>831.34004469493925</v>
-      </c>
-    </row>
-    <row r="533" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="533" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A533">
         <v>4506.68923613271</v>
       </c>
@@ -14718,12 +12354,8 @@
       <c r="F533">
         <v>-242.48449955654101</v>
       </c>
-      <c r="H533">
-        <f t="shared" si="8"/>
-        <v>1587.2821123753622</v>
-      </c>
-    </row>
-    <row r="534" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="534" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A534">
         <v>4523.28809233018</v>
       </c>
@@ -14742,12 +12374,8 @@
       <c r="F534">
         <v>-3773.8817228020298</v>
       </c>
-      <c r="H534">
-        <f t="shared" si="8"/>
-        <v>914.37287245701873</v>
-      </c>
-    </row>
-    <row r="535" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="535" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A535">
         <v>4527.4852192194503</v>
       </c>
@@ -14766,12 +12394,8 @@
       <c r="F535">
         <v>-2657.3838781260902</v>
       </c>
-      <c r="H535">
-        <f t="shared" si="8"/>
-        <v>1184.4777103047429</v>
-      </c>
-    </row>
-    <row r="536" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="536" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A536">
         <v>4546.0657245879502</v>
       </c>
@@ -14790,12 +12414,8 @@
       <c r="F536">
         <v>1192.4649668050299</v>
       </c>
-      <c r="H536">
-        <f t="shared" si="8"/>
-        <v>525.69738204906821</v>
-      </c>
-    </row>
-    <row r="537" spans="1:8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="537" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A537">
         <v>4671.5670138695896</v>
       </c>
@@ -14813,10 +12433,6 @@
       </c>
       <c r="F537">
         <v>-410.884225856586</v>
-      </c>
-      <c r="H537">
-        <f t="shared" si="8"/>
-        <v>577.20367803486477</v>
       </c>
     </row>
   </sheetData>
